--- a/data/actual/clausura26.xlsx
+++ b/data/actual/clausura26.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fecha 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fecha 2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -86,7 +87,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -108,17 +109,90 @@
         <color rgb="00B0BEC5"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B0BEC5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0BEC5"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0BEC5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B0BEC5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0BEC5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0BEC5"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0BEC5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0BEC5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -523,6 +597,8 @@
           <t xml:space="preserve">  Club Atlético Belgrano  vs  Rosario Central</t>
         </is>
       </c>
+      <c r="B1" s="11" t="n"/>
+      <c r="C1" s="12" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -935,6 +1011,8 @@
           <t xml:space="preserve">  📊 Métricas derivadas (para modelo predictivo)</t>
         </is>
       </c>
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="12" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -1156,6 +1234,8 @@
           <t xml:space="preserve">  Sarmiento  vs  Argentinos Juniors</t>
         </is>
       </c>
+      <c r="B44" s="11" t="n"/>
+      <c r="C44" s="12" t="n"/>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
@@ -1568,6 +1648,8 @@
           <t xml:space="preserve">  📊 Métricas derivadas (para modelo predictivo)</t>
         </is>
       </c>
+      <c r="B70" s="11" t="n"/>
+      <c r="C70" s="12" t="n"/>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
@@ -1789,6 +1871,8 @@
           <t xml:space="preserve">  Defensa y Justicia  vs  Aldosivi</t>
         </is>
       </c>
+      <c r="B87" s="11" t="n"/>
+      <c r="C87" s="12" t="n"/>
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
@@ -2184,6 +2268,8 @@
           <t xml:space="preserve">  📊 Métricas derivadas (para modelo predictivo)</t>
         </is>
       </c>
+      <c r="B112" s="11" t="n"/>
+      <c r="C112" s="12" t="n"/>
     </row>
     <row r="113" ht="20" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
@@ -2405,6 +2491,8 @@
           <t xml:space="preserve">  Gimnasia y Esgrima Mendoza  vs  Central Córdoba</t>
         </is>
       </c>
+      <c r="B129" s="11" t="n"/>
+      <c r="C129" s="12" t="n"/>
     </row>
     <row r="130" ht="20" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
@@ -2817,6 +2905,8 @@
           <t xml:space="preserve">  📊 Métricas derivadas (para modelo predictivo)</t>
         </is>
       </c>
+      <c r="B155" s="11" t="n"/>
+      <c r="C155" s="12" t="n"/>
     </row>
     <row r="156" ht="20" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
@@ -3038,6 +3128,8 @@
           <t xml:space="preserve">  Racing Club  vs  Gimnasia y Esgrima</t>
         </is>
       </c>
+      <c r="B172" s="11" t="n"/>
+      <c r="C172" s="12" t="n"/>
     </row>
     <row r="173" ht="20" customHeight="1">
       <c r="A173" s="2" t="inlineStr">
@@ -3450,6 +3542,8 @@
           <t xml:space="preserve">  📊 Métricas derivadas (para modelo predictivo)</t>
         </is>
       </c>
+      <c r="B198" s="11" t="n"/>
+      <c r="C198" s="12" t="n"/>
     </row>
     <row r="199" ht="20" customHeight="1">
       <c r="A199" s="2" t="inlineStr">
@@ -3671,6 +3765,8 @@
           <t xml:space="preserve">  Vélez Sarsfield  vs  Instituto De Córdoba</t>
         </is>
       </c>
+      <c r="B215" s="11" t="n"/>
+      <c r="C215" s="12" t="n"/>
     </row>
     <row r="216" ht="20" customHeight="1">
       <c r="A216" s="2" t="inlineStr">
@@ -4083,6 +4179,8 @@
           <t xml:space="preserve">  📊 Métricas derivadas (para modelo predictivo)</t>
         </is>
       </c>
+      <c r="B241" s="11" t="n"/>
+      <c r="C241" s="12" t="n"/>
     </row>
     <row r="242" ht="20" customHeight="1">
       <c r="A242" s="2" t="inlineStr">
@@ -4304,6 +4402,8 @@
           <t xml:space="preserve">  Club Atlético Platense  vs  Club Atlético Unión de Santa Fe</t>
         </is>
       </c>
+      <c r="B258" s="11" t="n"/>
+      <c r="C258" s="12" t="n"/>
     </row>
     <row r="259" ht="20" customHeight="1">
       <c r="A259" s="2" t="inlineStr">
@@ -4716,6 +4816,8 @@
           <t xml:space="preserve">  📊 Métricas derivadas (para modelo predictivo)</t>
         </is>
       </c>
+      <c r="B284" s="11" t="n"/>
+      <c r="C284" s="12" t="n"/>
     </row>
     <row r="285" ht="20" customHeight="1">
       <c r="A285" s="2" t="inlineStr">
@@ -4937,6 +5039,8 @@
           <t xml:space="preserve">  Huracán  vs  Banfield</t>
         </is>
       </c>
+      <c r="B301" s="11" t="n"/>
+      <c r="C301" s="12" t="n"/>
     </row>
     <row r="302" ht="20" customHeight="1">
       <c r="A302" s="2" t="inlineStr">
@@ -5349,6 +5453,8 @@
           <t xml:space="preserve">  📊 Métricas derivadas (para modelo predictivo)</t>
         </is>
       </c>
+      <c r="B327" s="11" t="n"/>
+      <c r="C327" s="12" t="n"/>
     </row>
     <row r="328" ht="20" customHeight="1">
       <c r="A328" s="2" t="inlineStr">
@@ -5570,6 +5676,8 @@
           <t xml:space="preserve">  Estudiantes de Río Cuarto  vs  Tigre</t>
         </is>
       </c>
+      <c r="B344" s="11" t="n"/>
+      <c r="C344" s="12" t="n"/>
     </row>
     <row r="345" ht="20" customHeight="1">
       <c r="A345" s="2" t="inlineStr">
@@ -5982,6 +6090,8 @@
           <t xml:space="preserve">  📊 Métricas derivadas (para modelo predictivo)</t>
         </is>
       </c>
+      <c r="B370" s="11" t="n"/>
+      <c r="C370" s="12" t="n"/>
     </row>
     <row r="371" ht="20" customHeight="1">
       <c r="A371" s="2" t="inlineStr">
@@ -6203,6 +6313,8 @@
           <t xml:space="preserve">  Newell's Old Boys  vs  CA Talleres</t>
         </is>
       </c>
+      <c r="B387" s="11" t="n"/>
+      <c r="C387" s="12" t="n"/>
     </row>
     <row r="388" ht="20" customHeight="1">
       <c r="A388" s="2" t="inlineStr">
@@ -6632,6 +6744,8 @@
           <t xml:space="preserve">  📊 Métricas derivadas (para modelo predictivo)</t>
         </is>
       </c>
+      <c r="B414" s="11" t="n"/>
+      <c r="C414" s="12" t="n"/>
     </row>
     <row r="415" ht="20" customHeight="1">
       <c r="A415" s="2" t="inlineStr">
@@ -6853,6 +6967,8 @@
           <t xml:space="preserve">  River Plate  vs  Barracas Central</t>
         </is>
       </c>
+      <c r="B431" s="11" t="n"/>
+      <c r="C431" s="12" t="n"/>
     </row>
     <row r="432" ht="20" customHeight="1">
       <c r="A432" s="2" t="inlineStr">
@@ -7265,6 +7381,8 @@
           <t xml:space="preserve">  📊 Métricas derivadas (para modelo predictivo)</t>
         </is>
       </c>
+      <c r="B457" s="11" t="n"/>
+      <c r="C457" s="12" t="n"/>
     </row>
     <row r="458" ht="20" customHeight="1">
       <c r="A458" s="2" t="inlineStr">
@@ -7486,6 +7604,8 @@
           <t xml:space="preserve">  CA Lanús  vs  San Lorenzo</t>
         </is>
       </c>
+      <c r="B474" s="11" t="n"/>
+      <c r="C474" s="12" t="n"/>
     </row>
     <row r="475" ht="20" customHeight="1">
       <c r="A475" s="2" t="inlineStr">
@@ -7898,6 +8018,8 @@
           <t xml:space="preserve">  📊 Métricas derivadas (para modelo predictivo)</t>
         </is>
       </c>
+      <c r="B500" s="11" t="n"/>
+      <c r="C500" s="12" t="n"/>
     </row>
     <row r="501" ht="20" customHeight="1">
       <c r="A501" s="2" t="inlineStr">
@@ -8119,6 +8241,8 @@
           <t xml:space="preserve">  Atlético Tucumán  vs  Independiente Rivadavia</t>
         </is>
       </c>
+      <c r="B517" s="11" t="n"/>
+      <c r="C517" s="12" t="n"/>
     </row>
     <row r="518" ht="20" customHeight="1">
       <c r="A518" s="2" t="inlineStr">
@@ -8497,6 +8621,8 @@
           <t xml:space="preserve">  📊 Métricas derivadas (para modelo predictivo)</t>
         </is>
       </c>
+      <c r="B541" s="11" t="n"/>
+      <c r="C541" s="12" t="n"/>
     </row>
     <row r="542" ht="20" customHeight="1">
       <c r="A542" s="2" t="inlineStr">
@@ -8718,6 +8844,8 @@
           <t xml:space="preserve">  Estudiantes de La Plata  vs  CA Independiente</t>
         </is>
       </c>
+      <c r="B558" s="11" t="n"/>
+      <c r="C558" s="12" t="n"/>
     </row>
     <row r="559" ht="20" customHeight="1">
       <c r="A559" s="2" t="inlineStr">
@@ -9130,6 +9258,8 @@
           <t xml:space="preserve">  📊 Métricas derivadas (para modelo predictivo)</t>
         </is>
       </c>
+      <c r="B584" s="11" t="n"/>
+      <c r="C584" s="12" t="n"/>
     </row>
     <row r="585" ht="20" customHeight="1">
       <c r="A585" s="2" t="inlineStr">
@@ -9351,6 +9481,8 @@
           <t xml:space="preserve">  Deportivo Riestra  vs  Boca Juniors</t>
         </is>
       </c>
+      <c r="B601" s="11" t="n"/>
+      <c r="C601" s="12" t="n"/>
     </row>
     <row r="602" ht="20" customHeight="1">
       <c r="A602" s="2" t="inlineStr">
@@ -9746,6 +9878,8 @@
           <t xml:space="preserve">  📊 Métricas derivadas (para modelo predictivo)</t>
         </is>
       </c>
+      <c r="B626" s="11" t="n"/>
+      <c r="C626" s="12" t="n"/>
     </row>
     <row r="627" ht="20" customHeight="1">
       <c r="A627" s="2" t="inlineStr">
@@ -9994,4 +10128,7643 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C514"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Banfield  vs  Sarmiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Banfield</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Sarmiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Posesión de balón</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>Goles esperados (xG)</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>Tiros totales</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>Tiros al arco</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Tiros afuera</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>Tiros bloqueados</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Córners</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>Fueras de juego</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>Faltas</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>Tarjetas amarillas</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>Pases totales</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>389</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>Pases precisos</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Atajadas del arquero</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>Quites</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Ocasiones claras</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>Ocasiones claras falladas</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>Regates intentados</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>3/16 (19%)</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>7/26 (27%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>Tiros dentro del área</t>
+        </is>
+      </c>
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>Tiros fuera del área</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>Goles evitados (arquero)</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1"/>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  📊 Métricas derivadas (para modelo predictivo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Métrica calculada</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Banfield</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Sarmiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>Precisión de tiros - Local (%)</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>Precisión de tiros - Visitante (%)</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="C30" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>xG por tiro - Local</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>xG por tiro - Visitante</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="C32" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>Eficiencia oportunidades claras - Local (%)</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>Eficiencia oportunidades claras - Visitante (%)</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="20" t="inlineStr">
+        <is>
+          <t>% Regates exitosos - Local</t>
+        </is>
+      </c>
+      <c r="B35" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>% Regates exitosos - Visitante</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t>% Duelos ganados - Local</t>
+        </is>
+      </c>
+      <c r="B37" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>% Duelos ganados - Visitante</t>
+        </is>
+      </c>
+      <c r="B38" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="20" t="inlineStr">
+        <is>
+          <t>Diferencial xG (Local - Visitante)</t>
+        </is>
+      </c>
+      <c r="B39" s="21" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="C39" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>% Tiros dentro del área - Local</t>
+        </is>
+      </c>
+      <c r="B40" s="18" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="C40" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>% Tiros dentro del área - Visitante</t>
+        </is>
+      </c>
+      <c r="B41" s="21" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="C41" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1"/>
+    <row r="43" ht="20" customHeight="1"/>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  San Lorenzo  vs  Gimnasia y Esgrima Mendoza</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>San Lorenzo</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Gimnasia y Esgrima Mendoza</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="15" t="inlineStr">
+        <is>
+          <t>Posesión de balón</t>
+        </is>
+      </c>
+      <c r="B47" s="16" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="17" t="inlineStr">
+        <is>
+          <t>Goles esperados (xG)</t>
+        </is>
+      </c>
+      <c r="B48" s="18" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="C48" s="18" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="15" t="inlineStr">
+        <is>
+          <t>Tiros totales</t>
+        </is>
+      </c>
+      <c r="B49" s="16" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="17" t="inlineStr">
+        <is>
+          <t>Tiros al arco</t>
+        </is>
+      </c>
+      <c r="B50" s="18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="15" t="inlineStr">
+        <is>
+          <t>Tiros afuera</t>
+        </is>
+      </c>
+      <c r="B51" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="17" t="inlineStr">
+        <is>
+          <t>Tiros bloqueados</t>
+        </is>
+      </c>
+      <c r="B52" s="18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C52" s="18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t>Córners</t>
+        </is>
+      </c>
+      <c r="B53" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C53" s="16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="17" t="inlineStr">
+        <is>
+          <t>Fueras de juego</t>
+        </is>
+      </c>
+      <c r="B54" s="18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C54" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="15" t="inlineStr">
+        <is>
+          <t>Faltas</t>
+        </is>
+      </c>
+      <c r="B55" s="16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C55" s="16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t>Tarjetas amarillas</t>
+        </is>
+      </c>
+      <c r="B56" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="15" t="inlineStr">
+        <is>
+          <t>Pases totales</t>
+        </is>
+      </c>
+      <c r="B57" s="16" t="inlineStr">
+        <is>
+          <t>446</t>
+        </is>
+      </c>
+      <c r="C57" s="16" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="17" t="inlineStr">
+        <is>
+          <t>Pases precisos</t>
+        </is>
+      </c>
+      <c r="B58" s="18" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="15" t="inlineStr">
+        <is>
+          <t>Atajadas del arquero</t>
+        </is>
+      </c>
+      <c r="B59" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C59" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="17" t="inlineStr">
+        <is>
+          <t>Quites</t>
+        </is>
+      </c>
+      <c r="B60" s="18" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="15" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="B61" s="16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C61" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="17" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="B62" s="18" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="15" t="inlineStr">
+        <is>
+          <t>Ocasiones claras</t>
+        </is>
+      </c>
+      <c r="B63" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C63" s="16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="17" t="inlineStr">
+        <is>
+          <t>Ocasiones claras falladas</t>
+        </is>
+      </c>
+      <c r="B64" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C64" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="15" t="inlineStr">
+        <is>
+          <t>Regates intentados</t>
+        </is>
+      </c>
+      <c r="B65" s="16" t="inlineStr">
+        <is>
+          <t>11/22 (50%)</t>
+        </is>
+      </c>
+      <c r="C65" s="16" t="inlineStr">
+        <is>
+          <t>6/29 (21%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="17" t="inlineStr">
+        <is>
+          <t>Tiros dentro del área</t>
+        </is>
+      </c>
+      <c r="B66" s="18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C66" s="18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="15" t="inlineStr">
+        <is>
+          <t>Tiros fuera del área</t>
+        </is>
+      </c>
+      <c r="B67" s="16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C67" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="17" t="inlineStr">
+        <is>
+          <t>Goles evitados (arquero)</t>
+        </is>
+      </c>
+      <c r="B68" s="18" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="C68" s="18" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1"/>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  📊 Métricas derivadas (para modelo predictivo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Métrica calculada</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>San Lorenzo</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Gimnasia y Esgrima Mendoza</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="20" t="inlineStr">
+        <is>
+          <t>Precisión de tiros - Local (%)</t>
+        </is>
+      </c>
+      <c r="B72" s="21" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="C72" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="17" t="inlineStr">
+        <is>
+          <t>Precisión de tiros - Visitante (%)</t>
+        </is>
+      </c>
+      <c r="B73" s="18" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="C73" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="20" t="inlineStr">
+        <is>
+          <t>xG por tiro - Local</t>
+        </is>
+      </c>
+      <c r="B74" s="21" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C74" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="17" t="inlineStr">
+        <is>
+          <t>xG por tiro - Visitante</t>
+        </is>
+      </c>
+      <c r="B75" s="18" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="C75" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="20" t="inlineStr">
+        <is>
+          <t>Eficiencia oportunidades claras - Local (%)</t>
+        </is>
+      </c>
+      <c r="B76" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="17" t="inlineStr">
+        <is>
+          <t>Eficiencia oportunidades claras - Visitante (%)</t>
+        </is>
+      </c>
+      <c r="B77" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="20" t="inlineStr">
+        <is>
+          <t>% Regates exitosos - Local</t>
+        </is>
+      </c>
+      <c r="B78" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="17" t="inlineStr">
+        <is>
+          <t>% Regates exitosos - Visitante</t>
+        </is>
+      </c>
+      <c r="B79" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="20" t="inlineStr">
+        <is>
+          <t>% Duelos ganados - Local</t>
+        </is>
+      </c>
+      <c r="B80" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="17" t="inlineStr">
+        <is>
+          <t>% Duelos ganados - Visitante</t>
+        </is>
+      </c>
+      <c r="B81" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="20" t="inlineStr">
+        <is>
+          <t>Diferencial xG (Local - Visitante)</t>
+        </is>
+      </c>
+      <c r="B82" s="21" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="C82" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="17" t="inlineStr">
+        <is>
+          <t>% Tiros dentro del área - Local</t>
+        </is>
+      </c>
+      <c r="B83" s="18" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="C83" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="20" t="inlineStr">
+        <is>
+          <t>% Tiros dentro del área - Visitante</t>
+        </is>
+      </c>
+      <c r="B84" s="21" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="C84" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1"/>
+    <row r="86" ht="20" customHeight="1"/>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Argentinos Juniors  vs  Estudiantes de Río Cuarto</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Estudiantes de Río Cuarto</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="14" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="B89" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C89" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="15" t="inlineStr">
+        <is>
+          <t>Posesión de balón</t>
+        </is>
+      </c>
+      <c r="B90" s="16" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="C90" s="16" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="17" t="inlineStr">
+        <is>
+          <t>Goles esperados (xG)</t>
+        </is>
+      </c>
+      <c r="B91" s="18" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C91" s="18" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="15" t="inlineStr">
+        <is>
+          <t>Tiros totales</t>
+        </is>
+      </c>
+      <c r="B92" s="16" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C92" s="16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="17" t="inlineStr">
+        <is>
+          <t>Tiros al arco</t>
+        </is>
+      </c>
+      <c r="B93" s="18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C93" s="18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="15" t="inlineStr">
+        <is>
+          <t>Tiros afuera</t>
+        </is>
+      </c>
+      <c r="B94" s="16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C94" s="16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="17" t="inlineStr">
+        <is>
+          <t>Tiros bloqueados</t>
+        </is>
+      </c>
+      <c r="B95" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C95" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="15" t="inlineStr">
+        <is>
+          <t>Córners</t>
+        </is>
+      </c>
+      <c r="B96" s="16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C96" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="17" t="inlineStr">
+        <is>
+          <t>Fueras de juego</t>
+        </is>
+      </c>
+      <c r="B97" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C97" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="15" t="inlineStr">
+        <is>
+          <t>Faltas</t>
+        </is>
+      </c>
+      <c r="B98" s="16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C98" s="16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="17" t="inlineStr">
+        <is>
+          <t>Tarjetas amarillas</t>
+        </is>
+      </c>
+      <c r="B99" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C99" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="15" t="inlineStr">
+        <is>
+          <t>Pases totales</t>
+        </is>
+      </c>
+      <c r="B100" s="16" t="inlineStr">
+        <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="C100" s="16" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="17" t="inlineStr">
+        <is>
+          <t>Pases precisos</t>
+        </is>
+      </c>
+      <c r="B101" s="18" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="C101" s="18" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="15" t="inlineStr">
+        <is>
+          <t>Atajadas del arquero</t>
+        </is>
+      </c>
+      <c r="B102" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C102" s="16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="17" t="inlineStr">
+        <is>
+          <t>Quites</t>
+        </is>
+      </c>
+      <c r="B103" s="18" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C103" s="18" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="15" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="B104" s="16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C104" s="16" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="17" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="B105" s="18" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C105" s="18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="15" t="inlineStr">
+        <is>
+          <t>Ocasiones claras</t>
+        </is>
+      </c>
+      <c r="B106" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C106" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="17" t="inlineStr">
+        <is>
+          <t>Ocasiones claras falladas</t>
+        </is>
+      </c>
+      <c r="B107" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C107" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="15" t="inlineStr">
+        <is>
+          <t>Regates intentados</t>
+        </is>
+      </c>
+      <c r="B108" s="16" t="inlineStr">
+        <is>
+          <t>12/23 (52%)</t>
+        </is>
+      </c>
+      <c r="C108" s="16" t="inlineStr">
+        <is>
+          <t>7/18 (39%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="17" t="inlineStr">
+        <is>
+          <t>Tiros dentro del área</t>
+        </is>
+      </c>
+      <c r="B109" s="18" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C109" s="18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="15" t="inlineStr">
+        <is>
+          <t>Tiros fuera del área</t>
+        </is>
+      </c>
+      <c r="B110" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C110" s="16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="17" t="inlineStr">
+        <is>
+          <t>Goles evitados (arquero)</t>
+        </is>
+      </c>
+      <c r="B111" s="18" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="C111" s="18" t="inlineStr">
+        <is>
+          <t>-0.72</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1"/>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  📊 Métricas derivadas (para modelo predictivo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Métrica calculada</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Estudiantes de Río Cuarto</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="20" t="inlineStr">
+        <is>
+          <t>Precisión de tiros - Local (%)</t>
+        </is>
+      </c>
+      <c r="B115" s="21" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="C115" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="17" t="inlineStr">
+        <is>
+          <t>Precisión de tiros - Visitante (%)</t>
+        </is>
+      </c>
+      <c r="B116" s="18" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="C116" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="20" t="inlineStr">
+        <is>
+          <t>xG por tiro - Local</t>
+        </is>
+      </c>
+      <c r="B117" s="21" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="C117" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="17" t="inlineStr">
+        <is>
+          <t>xG por tiro - Visitante</t>
+        </is>
+      </c>
+      <c r="B118" s="18" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C118" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="20" t="inlineStr">
+        <is>
+          <t>Eficiencia oportunidades claras - Local (%)</t>
+        </is>
+      </c>
+      <c r="B119" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C119" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="17" t="inlineStr">
+        <is>
+          <t>Eficiencia oportunidades claras - Visitante (%)</t>
+        </is>
+      </c>
+      <c r="B120" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="20" t="inlineStr">
+        <is>
+          <t>% Regates exitosos - Local</t>
+        </is>
+      </c>
+      <c r="B121" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="17" t="inlineStr">
+        <is>
+          <t>% Regates exitosos - Visitante</t>
+        </is>
+      </c>
+      <c r="B122" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="20" t="inlineStr">
+        <is>
+          <t>% Duelos ganados - Local</t>
+        </is>
+      </c>
+      <c r="B123" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="17" t="inlineStr">
+        <is>
+          <t>% Duelos ganados - Visitante</t>
+        </is>
+      </c>
+      <c r="B124" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="20" t="inlineStr">
+        <is>
+          <t>Diferencial xG (Local - Visitante)</t>
+        </is>
+      </c>
+      <c r="B125" s="21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="C125" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="17" t="inlineStr">
+        <is>
+          <t>% Tiros dentro del área - Local</t>
+        </is>
+      </c>
+      <c r="B126" s="18" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="C126" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="20" t="inlineStr">
+        <is>
+          <t>% Tiros dentro del área - Visitante</t>
+        </is>
+      </c>
+      <c r="B127" s="21" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="C127" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1"/>
+    <row r="129" ht="20" customHeight="1"/>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Rosario Central  vs  Racing Club</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Racing Club</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="14" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="B132" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C132" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" ht="20" customHeight="1">
+      <c r="A133" s="15" t="inlineStr">
+        <is>
+          <t>Posesión de balón</t>
+        </is>
+      </c>
+      <c r="B133" s="16" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="C133" s="16" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="20" customHeight="1">
+      <c r="A134" s="17" t="inlineStr">
+        <is>
+          <t>Goles esperados (xG)</t>
+        </is>
+      </c>
+      <c r="B134" s="18" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="C134" s="18" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="15" t="inlineStr">
+        <is>
+          <t>Tiros totales</t>
+        </is>
+      </c>
+      <c r="B135" s="16" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C135" s="16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="20" customHeight="1">
+      <c r="A136" s="17" t="inlineStr">
+        <is>
+          <t>Tiros al arco</t>
+        </is>
+      </c>
+      <c r="B136" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C136" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="20" customHeight="1">
+      <c r="A137" s="15" t="inlineStr">
+        <is>
+          <t>Tiros afuera</t>
+        </is>
+      </c>
+      <c r="B137" s="16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C137" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="20" customHeight="1">
+      <c r="A138" s="17" t="inlineStr">
+        <is>
+          <t>Tiros bloqueados</t>
+        </is>
+      </c>
+      <c r="B138" s="18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C138" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="20" customHeight="1">
+      <c r="A139" s="15" t="inlineStr">
+        <is>
+          <t>Córners</t>
+        </is>
+      </c>
+      <c r="B139" s="16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C139" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="20" customHeight="1">
+      <c r="A140" s="17" t="inlineStr">
+        <is>
+          <t>Fueras de juego</t>
+        </is>
+      </c>
+      <c r="B140" s="18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C140" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="20" customHeight="1">
+      <c r="A141" s="15" t="inlineStr">
+        <is>
+          <t>Faltas</t>
+        </is>
+      </c>
+      <c r="B141" s="16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C141" s="16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="20" customHeight="1">
+      <c r="A142" s="17" t="inlineStr">
+        <is>
+          <t>Tarjetas amarillas</t>
+        </is>
+      </c>
+      <c r="B142" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C142" s="18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="20" customHeight="1">
+      <c r="A143" s="15" t="inlineStr">
+        <is>
+          <t>Pases totales</t>
+        </is>
+      </c>
+      <c r="B143" s="16" t="inlineStr">
+        <is>
+          <t>441</t>
+        </is>
+      </c>
+      <c r="C143" s="16" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="20" customHeight="1">
+      <c r="A144" s="17" t="inlineStr">
+        <is>
+          <t>Pases precisos</t>
+        </is>
+      </c>
+      <c r="B144" s="18" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="C144" s="18" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="20" customHeight="1">
+      <c r="A145" s="15" t="inlineStr">
+        <is>
+          <t>Atajadas del arquero</t>
+        </is>
+      </c>
+      <c r="B145" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C145" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="20" customHeight="1">
+      <c r="A146" s="17" t="inlineStr">
+        <is>
+          <t>Quites</t>
+        </is>
+      </c>
+      <c r="B146" s="18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C146" s="18" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="20" customHeight="1">
+      <c r="A147" s="15" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="B147" s="16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C147" s="16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="20" customHeight="1">
+      <c r="A148" s="17" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="B148" s="18" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C148" s="18" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="20" customHeight="1">
+      <c r="A149" s="15" t="inlineStr">
+        <is>
+          <t>Ocasiones claras</t>
+        </is>
+      </c>
+      <c r="B149" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C149" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="20" customHeight="1">
+      <c r="A150" s="17" t="inlineStr">
+        <is>
+          <t>Ocasiones claras falladas</t>
+        </is>
+      </c>
+      <c r="B150" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C150" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="20" customHeight="1">
+      <c r="A151" s="15" t="inlineStr">
+        <is>
+          <t>Regates intentados</t>
+        </is>
+      </c>
+      <c r="B151" s="16" t="inlineStr">
+        <is>
+          <t>6/23 (26%)</t>
+        </is>
+      </c>
+      <c r="C151" s="16" t="inlineStr">
+        <is>
+          <t>6/11 (55%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="20" customHeight="1">
+      <c r="A152" s="17" t="inlineStr">
+        <is>
+          <t>Tiros dentro del área</t>
+        </is>
+      </c>
+      <c r="B152" s="18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C152" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="20" customHeight="1">
+      <c r="A153" s="15" t="inlineStr">
+        <is>
+          <t>Tiros fuera del área</t>
+        </is>
+      </c>
+      <c r="B153" s="16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C153" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="20" customHeight="1">
+      <c r="A154" s="17" t="inlineStr">
+        <is>
+          <t>Goles evitados (arquero)</t>
+        </is>
+      </c>
+      <c r="B154" s="18" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="C154" s="18" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="20" customHeight="1"/>
+    <row r="156" ht="20" customHeight="1">
+      <c r="A156" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  📊 Métricas derivadas (para modelo predictivo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="20" customHeight="1">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Métrica calculada</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Racing Club</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="20" customHeight="1">
+      <c r="A158" s="20" t="inlineStr">
+        <is>
+          <t>Precisión de tiros - Local (%)</t>
+        </is>
+      </c>
+      <c r="B158" s="21" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="C158" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="20" customHeight="1">
+      <c r="A159" s="17" t="inlineStr">
+        <is>
+          <t>Precisión de tiros - Visitante (%)</t>
+        </is>
+      </c>
+      <c r="B159" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="C159" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="20" customHeight="1">
+      <c r="A160" s="20" t="inlineStr">
+        <is>
+          <t>xG por tiro - Local</t>
+        </is>
+      </c>
+      <c r="B160" s="21" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="C160" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="20" customHeight="1">
+      <c r="A161" s="17" t="inlineStr">
+        <is>
+          <t>xG por tiro - Visitante</t>
+        </is>
+      </c>
+      <c r="B161" s="18" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="C161" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="20" customHeight="1">
+      <c r="A162" s="20" t="inlineStr">
+        <is>
+          <t>Eficiencia oportunidades claras - Local (%)</t>
+        </is>
+      </c>
+      <c r="B162" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C162" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="20" customHeight="1">
+      <c r="A163" s="17" t="inlineStr">
+        <is>
+          <t>Eficiencia oportunidades claras - Visitante (%)</t>
+        </is>
+      </c>
+      <c r="B163" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C163" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="20" customHeight="1">
+      <c r="A164" s="20" t="inlineStr">
+        <is>
+          <t>% Regates exitosos - Local</t>
+        </is>
+      </c>
+      <c r="B164" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C164" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="20" customHeight="1">
+      <c r="A165" s="17" t="inlineStr">
+        <is>
+          <t>% Regates exitosos - Visitante</t>
+        </is>
+      </c>
+      <c r="B165" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C165" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="20" customHeight="1">
+      <c r="A166" s="20" t="inlineStr">
+        <is>
+          <t>% Duelos ganados - Local</t>
+        </is>
+      </c>
+      <c r="B166" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C166" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="20" customHeight="1">
+      <c r="A167" s="17" t="inlineStr">
+        <is>
+          <t>% Duelos ganados - Visitante</t>
+        </is>
+      </c>
+      <c r="B167" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C167" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="20" customHeight="1">
+      <c r="A168" s="20" t="inlineStr">
+        <is>
+          <t>Diferencial xG (Local - Visitante)</t>
+        </is>
+      </c>
+      <c r="B168" s="21" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C168" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="20" customHeight="1">
+      <c r="A169" s="17" t="inlineStr">
+        <is>
+          <t>% Tiros dentro del área - Local</t>
+        </is>
+      </c>
+      <c r="B169" s="18" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="C169" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="20" customHeight="1">
+      <c r="A170" s="20" t="inlineStr">
+        <is>
+          <t>% Tiros dentro del área - Visitante</t>
+        </is>
+      </c>
+      <c r="B170" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="C170" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="20" customHeight="1"/>
+    <row r="172" ht="20" customHeight="1"/>
+    <row r="173" ht="20" customHeight="1">
+      <c r="A173" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Barracas Central  vs  Aldosivi</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="20" customHeight="1">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Barracas Central</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Aldosivi</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="20" customHeight="1">
+      <c r="A175" s="14" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="B175" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C175" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" ht="20" customHeight="1">
+      <c r="A176" s="15" t="inlineStr">
+        <is>
+          <t>Posesión de balón</t>
+        </is>
+      </c>
+      <c r="B176" s="16" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="C176" s="16" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="20" customHeight="1">
+      <c r="A177" s="17" t="inlineStr">
+        <is>
+          <t>Goles esperados (xG)</t>
+        </is>
+      </c>
+      <c r="B177" s="18" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="C177" s="18" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="20" customHeight="1">
+      <c r="A178" s="15" t="inlineStr">
+        <is>
+          <t>Tiros totales</t>
+        </is>
+      </c>
+      <c r="B178" s="16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C178" s="16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="20" customHeight="1">
+      <c r="A179" s="17" t="inlineStr">
+        <is>
+          <t>Tiros al arco</t>
+        </is>
+      </c>
+      <c r="B179" s="18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C179" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="20" customHeight="1">
+      <c r="A180" s="15" t="inlineStr">
+        <is>
+          <t>Tiros afuera</t>
+        </is>
+      </c>
+      <c r="B180" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C180" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="20" customHeight="1">
+      <c r="A181" s="17" t="inlineStr">
+        <is>
+          <t>Tiros bloqueados</t>
+        </is>
+      </c>
+      <c r="B181" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C181" s="18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="20" customHeight="1">
+      <c r="A182" s="15" t="inlineStr">
+        <is>
+          <t>Córners</t>
+        </is>
+      </c>
+      <c r="B182" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C182" s="16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="20" customHeight="1">
+      <c r="A183" s="17" t="inlineStr">
+        <is>
+          <t>Fueras de juego</t>
+        </is>
+      </c>
+      <c r="B183" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C183" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="20" customHeight="1">
+      <c r="A184" s="15" t="inlineStr">
+        <is>
+          <t>Faltas</t>
+        </is>
+      </c>
+      <c r="B184" s="16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C184" s="16" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="20" customHeight="1">
+      <c r="A185" s="17" t="inlineStr">
+        <is>
+          <t>Tarjetas amarillas</t>
+        </is>
+      </c>
+      <c r="B185" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C185" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="20" customHeight="1">
+      <c r="A186" s="15" t="inlineStr">
+        <is>
+          <t>Pases totales</t>
+        </is>
+      </c>
+      <c r="B186" s="16" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="C186" s="16" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="20" customHeight="1">
+      <c r="A187" s="17" t="inlineStr">
+        <is>
+          <t>Pases precisos</t>
+        </is>
+      </c>
+      <c r="B187" s="18" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="C187" s="18" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="20" customHeight="1">
+      <c r="A188" s="15" t="inlineStr">
+        <is>
+          <t>Atajadas del arquero</t>
+        </is>
+      </c>
+      <c r="B188" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C188" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="20" customHeight="1">
+      <c r="A189" s="17" t="inlineStr">
+        <is>
+          <t>Quites</t>
+        </is>
+      </c>
+      <c r="B189" s="18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C189" s="18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="20" customHeight="1">
+      <c r="A190" s="15" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="B190" s="16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C190" s="16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="20" customHeight="1">
+      <c r="A191" s="17" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="B191" s="18" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="C191" s="18" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="20" customHeight="1">
+      <c r="A192" s="15" t="inlineStr">
+        <is>
+          <t>Ocasiones claras</t>
+        </is>
+      </c>
+      <c r="B192" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C192" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="20" customHeight="1">
+      <c r="A193" s="17" t="inlineStr">
+        <is>
+          <t>Ocasiones claras falladas</t>
+        </is>
+      </c>
+      <c r="B193" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C193" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="20" customHeight="1">
+      <c r="A194" s="15" t="inlineStr">
+        <is>
+          <t>Regates intentados</t>
+        </is>
+      </c>
+      <c r="B194" s="16" t="inlineStr">
+        <is>
+          <t>6/15 (40%)</t>
+        </is>
+      </c>
+      <c r="C194" s="16" t="inlineStr">
+        <is>
+          <t>4/9 (44%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="20" customHeight="1">
+      <c r="A195" s="17" t="inlineStr">
+        <is>
+          <t>Tiros dentro del área</t>
+        </is>
+      </c>
+      <c r="B195" s="18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C195" s="18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="20" customHeight="1">
+      <c r="A196" s="15" t="inlineStr">
+        <is>
+          <t>Tiros fuera del área</t>
+        </is>
+      </c>
+      <c r="B196" s="16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C196" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="20" customHeight="1">
+      <c r="A197" s="17" t="inlineStr">
+        <is>
+          <t>Goles evitados (arquero)</t>
+        </is>
+      </c>
+      <c r="B197" s="18" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C197" s="18" t="inlineStr">
+        <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="20" customHeight="1"/>
+    <row r="199" ht="20" customHeight="1">
+      <c r="A199" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  📊 Métricas derivadas (para modelo predictivo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="20" customHeight="1">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Métrica calculada</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>Barracas Central</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>Aldosivi</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="20" customHeight="1">
+      <c r="A201" s="20" t="inlineStr">
+        <is>
+          <t>Precisión de tiros - Local (%)</t>
+        </is>
+      </c>
+      <c r="B201" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="C201" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="20" customHeight="1">
+      <c r="A202" s="17" t="inlineStr">
+        <is>
+          <t>Precisión de tiros - Visitante (%)</t>
+        </is>
+      </c>
+      <c r="B202" s="18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="C202" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="20" customHeight="1">
+      <c r="A203" s="20" t="inlineStr">
+        <is>
+          <t>xG por tiro - Local</t>
+        </is>
+      </c>
+      <c r="B203" s="21" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C203" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="20" customHeight="1">
+      <c r="A204" s="17" t="inlineStr">
+        <is>
+          <t>xG por tiro - Visitante</t>
+        </is>
+      </c>
+      <c r="B204" s="18" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="C204" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="20" customHeight="1">
+      <c r="A205" s="20" t="inlineStr">
+        <is>
+          <t>Eficiencia oportunidades claras - Local (%)</t>
+        </is>
+      </c>
+      <c r="B205" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C205" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="20" customHeight="1">
+      <c r="A206" s="17" t="inlineStr">
+        <is>
+          <t>Eficiencia oportunidades claras - Visitante (%)</t>
+        </is>
+      </c>
+      <c r="B206" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C206" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="20" customHeight="1">
+      <c r="A207" s="20" t="inlineStr">
+        <is>
+          <t>% Regates exitosos - Local</t>
+        </is>
+      </c>
+      <c r="B207" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C207" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="20" customHeight="1">
+      <c r="A208" s="17" t="inlineStr">
+        <is>
+          <t>% Regates exitosos - Visitante</t>
+        </is>
+      </c>
+      <c r="B208" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C208" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="20" customHeight="1">
+      <c r="A209" s="20" t="inlineStr">
+        <is>
+          <t>% Duelos ganados - Local</t>
+        </is>
+      </c>
+      <c r="B209" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C209" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="20" customHeight="1">
+      <c r="A210" s="17" t="inlineStr">
+        <is>
+          <t>% Duelos ganados - Visitante</t>
+        </is>
+      </c>
+      <c r="B210" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C210" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="20" customHeight="1">
+      <c r="A211" s="20" t="inlineStr">
+        <is>
+          <t>Diferencial xG (Local - Visitante)</t>
+        </is>
+      </c>
+      <c r="B211" s="21" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C211" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="20" customHeight="1">
+      <c r="A212" s="17" t="inlineStr">
+        <is>
+          <t>% Tiros dentro del área - Local</t>
+        </is>
+      </c>
+      <c r="B212" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="C212" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="20" customHeight="1">
+      <c r="A213" s="20" t="inlineStr">
+        <is>
+          <t>% Tiros dentro del área - Visitante</t>
+        </is>
+      </c>
+      <c r="B213" s="21" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="C213" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="20" customHeight="1"/>
+    <row r="215" ht="20" customHeight="1"/>
+    <row r="216" ht="20" customHeight="1">
+      <c r="A216" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Defensa y Justicia  vs  Deportivo Riestra</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="20" customHeight="1">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>Defensa y Justicia</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>Deportivo Riestra</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="20" customHeight="1">
+      <c r="A218" s="14" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="B218" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C218" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" ht="20" customHeight="1">
+      <c r="A219" s="15" t="inlineStr">
+        <is>
+          <t>Posesión de balón</t>
+        </is>
+      </c>
+      <c r="B219" s="16" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="C219" s="16" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="20" customHeight="1">
+      <c r="A220" s="17" t="inlineStr">
+        <is>
+          <t>Goles esperados (xG)</t>
+        </is>
+      </c>
+      <c r="B220" s="18" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C220" s="18" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="20" customHeight="1">
+      <c r="A221" s="15" t="inlineStr">
+        <is>
+          <t>Tiros totales</t>
+        </is>
+      </c>
+      <c r="B221" s="16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C221" s="16" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="20" customHeight="1">
+      <c r="A222" s="17" t="inlineStr">
+        <is>
+          <t>Tiros al arco</t>
+        </is>
+      </c>
+      <c r="B222" s="18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C222" s="18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="20" customHeight="1">
+      <c r="A223" s="15" t="inlineStr">
+        <is>
+          <t>Tiros afuera</t>
+        </is>
+      </c>
+      <c r="B223" s="16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C223" s="16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="20" customHeight="1">
+      <c r="A224" s="17" t="inlineStr">
+        <is>
+          <t>Tiros bloqueados</t>
+        </is>
+      </c>
+      <c r="B224" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C224" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="20" customHeight="1">
+      <c r="A225" s="15" t="inlineStr">
+        <is>
+          <t>Córners</t>
+        </is>
+      </c>
+      <c r="B225" s="16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C225" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="20" customHeight="1">
+      <c r="A226" s="17" t="inlineStr">
+        <is>
+          <t>Fueras de juego</t>
+        </is>
+      </c>
+      <c r="B226" s="18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C226" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="20" customHeight="1">
+      <c r="A227" s="15" t="inlineStr">
+        <is>
+          <t>Faltas</t>
+        </is>
+      </c>
+      <c r="B227" s="16" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C227" s="16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="20" customHeight="1">
+      <c r="A228" s="17" t="inlineStr">
+        <is>
+          <t>Tarjetas amarillas</t>
+        </is>
+      </c>
+      <c r="B228" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C228" s="18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="20" customHeight="1">
+      <c r="A229" s="15" t="inlineStr">
+        <is>
+          <t>Pases totales</t>
+        </is>
+      </c>
+      <c r="B229" s="16" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="C229" s="16" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="20" customHeight="1">
+      <c r="A230" s="17" t="inlineStr">
+        <is>
+          <t>Pases precisos</t>
+        </is>
+      </c>
+      <c r="B230" s="18" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="C230" s="18" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="20" customHeight="1">
+      <c r="A231" s="15" t="inlineStr">
+        <is>
+          <t>Atajadas del arquero</t>
+        </is>
+      </c>
+      <c r="B231" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C231" s="16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="20" customHeight="1">
+      <c r="A232" s="17" t="inlineStr">
+        <is>
+          <t>Quites</t>
+        </is>
+      </c>
+      <c r="B232" s="18" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C232" s="18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="20" customHeight="1">
+      <c r="A233" s="15" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="B233" s="16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C233" s="16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="20" customHeight="1">
+      <c r="A234" s="17" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="B234" s="18" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C234" s="18" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="20" customHeight="1">
+      <c r="A235" s="15" t="inlineStr">
+        <is>
+          <t>Ocasiones claras</t>
+        </is>
+      </c>
+      <c r="B235" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C235" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="20" customHeight="1">
+      <c r="A236" s="17" t="inlineStr">
+        <is>
+          <t>Ocasiones claras falladas</t>
+        </is>
+      </c>
+      <c r="B236" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C236" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="20" customHeight="1">
+      <c r="A237" s="15" t="inlineStr">
+        <is>
+          <t>Regates intentados</t>
+        </is>
+      </c>
+      <c r="B237" s="16" t="inlineStr">
+        <is>
+          <t>12/25 (48%)</t>
+        </is>
+      </c>
+      <c r="C237" s="16" t="inlineStr">
+        <is>
+          <t>8/16 (50%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="20" customHeight="1">
+      <c r="A238" s="17" t="inlineStr">
+        <is>
+          <t>Tiros dentro del área</t>
+        </is>
+      </c>
+      <c r="B238" s="18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C238" s="18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="20" customHeight="1">
+      <c r="A239" s="15" t="inlineStr">
+        <is>
+          <t>Tiros fuera del área</t>
+        </is>
+      </c>
+      <c r="B239" s="16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C239" s="16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="20" customHeight="1">
+      <c r="A240" s="17" t="inlineStr">
+        <is>
+          <t>Goles evitados (arquero)</t>
+        </is>
+      </c>
+      <c r="B240" s="18" t="inlineStr">
+        <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="C240" s="18" t="inlineStr">
+        <is>
+          <t>-0.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="20" customHeight="1"/>
+    <row r="242" ht="20" customHeight="1">
+      <c r="A242" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  📊 Métricas derivadas (para modelo predictivo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="20" customHeight="1">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>Métrica calculada</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>Defensa y Justicia</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>Deportivo Riestra</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="20" customHeight="1">
+      <c r="A244" s="20" t="inlineStr">
+        <is>
+          <t>Precisión de tiros - Local (%)</t>
+        </is>
+      </c>
+      <c r="B244" s="21" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="C244" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="20" customHeight="1">
+      <c r="A245" s="17" t="inlineStr">
+        <is>
+          <t>Precisión de tiros - Visitante (%)</t>
+        </is>
+      </c>
+      <c r="B245" s="18" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="C245" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="20" customHeight="1">
+      <c r="A246" s="20" t="inlineStr">
+        <is>
+          <t>xG por tiro - Local</t>
+        </is>
+      </c>
+      <c r="B246" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C246" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="20" customHeight="1">
+      <c r="A247" s="17" t="inlineStr">
+        <is>
+          <t>xG por tiro - Visitante</t>
+        </is>
+      </c>
+      <c r="B247" s="18" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="C247" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="20" customHeight="1">
+      <c r="A248" s="20" t="inlineStr">
+        <is>
+          <t>Eficiencia oportunidades claras - Local (%)</t>
+        </is>
+      </c>
+      <c r="B248" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C248" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="20" customHeight="1">
+      <c r="A249" s="17" t="inlineStr">
+        <is>
+          <t>Eficiencia oportunidades claras - Visitante (%)</t>
+        </is>
+      </c>
+      <c r="B249" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C249" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="20" customHeight="1">
+      <c r="A250" s="20" t="inlineStr">
+        <is>
+          <t>% Regates exitosos - Local</t>
+        </is>
+      </c>
+      <c r="B250" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C250" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="20" customHeight="1">
+      <c r="A251" s="17" t="inlineStr">
+        <is>
+          <t>% Regates exitosos - Visitante</t>
+        </is>
+      </c>
+      <c r="B251" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C251" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="20" customHeight="1">
+      <c r="A252" s="20" t="inlineStr">
+        <is>
+          <t>% Duelos ganados - Local</t>
+        </is>
+      </c>
+      <c r="B252" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C252" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="20" customHeight="1">
+      <c r="A253" s="17" t="inlineStr">
+        <is>
+          <t>% Duelos ganados - Visitante</t>
+        </is>
+      </c>
+      <c r="B253" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C253" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="20" customHeight="1">
+      <c r="A254" s="20" t="inlineStr">
+        <is>
+          <t>Diferencial xG (Local - Visitante)</t>
+        </is>
+      </c>
+      <c r="B254" s="21" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="C254" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="20" customHeight="1">
+      <c r="A255" s="17" t="inlineStr">
+        <is>
+          <t>% Tiros dentro del área - Local</t>
+        </is>
+      </c>
+      <c r="B255" s="18" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="C255" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="20" customHeight="1">
+      <c r="A256" s="20" t="inlineStr">
+        <is>
+          <t>% Tiros dentro del área - Visitante</t>
+        </is>
+      </c>
+      <c r="B256" s="21" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="C256" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="20" customHeight="1"/>
+    <row r="258" ht="20" customHeight="1"/>
+    <row r="259" ht="20" customHeight="1">
+      <c r="A259" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Gimnasia y Esgrima  vs  River Plate</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="20" customHeight="1">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>Gimnasia y Esgrima</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="20" customHeight="1">
+      <c r="A261" s="14" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="B261" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C261" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" ht="20" customHeight="1">
+      <c r="A262" s="15" t="inlineStr">
+        <is>
+          <t>Posesión de balón</t>
+        </is>
+      </c>
+      <c r="B262" s="16" t="inlineStr">
+        <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="C262" s="16" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="20" customHeight="1">
+      <c r="A263" s="17" t="inlineStr">
+        <is>
+          <t>Goles esperados (xG)</t>
+        </is>
+      </c>
+      <c r="B263" s="18" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="C263" s="18" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="20" customHeight="1">
+      <c r="A264" s="15" t="inlineStr">
+        <is>
+          <t>Tiros totales</t>
+        </is>
+      </c>
+      <c r="B264" s="16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C264" s="16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="20" customHeight="1">
+      <c r="A265" s="17" t="inlineStr">
+        <is>
+          <t>Tiros al arco</t>
+        </is>
+      </c>
+      <c r="B265" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C265" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="20" customHeight="1">
+      <c r="A266" s="15" t="inlineStr">
+        <is>
+          <t>Tiros afuera</t>
+        </is>
+      </c>
+      <c r="B266" s="16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C266" s="16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="20" customHeight="1">
+      <c r="A267" s="17" t="inlineStr">
+        <is>
+          <t>Tiros bloqueados</t>
+        </is>
+      </c>
+      <c r="B267" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C267" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="20" customHeight="1">
+      <c r="A268" s="15" t="inlineStr">
+        <is>
+          <t>Córners</t>
+        </is>
+      </c>
+      <c r="B268" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C268" s="16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="20" customHeight="1">
+      <c r="A269" s="17" t="inlineStr">
+        <is>
+          <t>Fueras de juego</t>
+        </is>
+      </c>
+      <c r="B269" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C269" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="20" customHeight="1">
+      <c r="A270" s="15" t="inlineStr">
+        <is>
+          <t>Faltas</t>
+        </is>
+      </c>
+      <c r="B270" s="16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C270" s="16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="20" customHeight="1">
+      <c r="A271" s="17" t="inlineStr">
+        <is>
+          <t>Tarjetas amarillas</t>
+        </is>
+      </c>
+      <c r="B271" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C271" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="20" customHeight="1">
+      <c r="A272" s="15" t="inlineStr">
+        <is>
+          <t>Pases totales</t>
+        </is>
+      </c>
+      <c r="B272" s="16" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="C272" s="16" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="20" customHeight="1">
+      <c r="A273" s="17" t="inlineStr">
+        <is>
+          <t>Pases precisos</t>
+        </is>
+      </c>
+      <c r="B273" s="18" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="C273" s="18" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="20" customHeight="1">
+      <c r="A274" s="15" t="inlineStr">
+        <is>
+          <t>Atajadas del arquero</t>
+        </is>
+      </c>
+      <c r="B274" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C274" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="20" customHeight="1">
+      <c r="A275" s="17" t="inlineStr">
+        <is>
+          <t>Quites</t>
+        </is>
+      </c>
+      <c r="B275" s="18" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C275" s="18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="20" customHeight="1">
+      <c r="A276" s="15" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="B276" s="16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C276" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="20" customHeight="1">
+      <c r="A277" s="17" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="B277" s="18" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C277" s="18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="20" customHeight="1">
+      <c r="A278" s="15" t="inlineStr">
+        <is>
+          <t>Ocasiones claras</t>
+        </is>
+      </c>
+      <c r="B278" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C278" s="16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="279" ht="20" customHeight="1">
+      <c r="A279" s="17" t="inlineStr">
+        <is>
+          <t>Ocasiones claras falladas</t>
+        </is>
+      </c>
+      <c r="B279" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C279" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="20" customHeight="1">
+      <c r="A280" s="15" t="inlineStr">
+        <is>
+          <t>Regates intentados</t>
+        </is>
+      </c>
+      <c r="B280" s="16" t="inlineStr">
+        <is>
+          <t>10/19 (53%)</t>
+        </is>
+      </c>
+      <c r="C280" s="16" t="inlineStr">
+        <is>
+          <t>10/24 (42%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="20" customHeight="1">
+      <c r="A281" s="17" t="inlineStr">
+        <is>
+          <t>Tiros dentro del área</t>
+        </is>
+      </c>
+      <c r="B281" s="18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C281" s="18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="20" customHeight="1">
+      <c r="A282" s="15" t="inlineStr">
+        <is>
+          <t>Tiros fuera del área</t>
+        </is>
+      </c>
+      <c r="B282" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C282" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="20" customHeight="1">
+      <c r="A283" s="17" t="inlineStr">
+        <is>
+          <t>Goles evitados (arquero)</t>
+        </is>
+      </c>
+      <c r="B283" s="18" t="inlineStr">
+        <is>
+          <t>0.41</t>
+        </is>
+      </c>
+      <c r="C283" s="18" t="inlineStr">
+        <is>
+          <t>-0.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="20" customHeight="1"/>
+    <row r="285" ht="20" customHeight="1">
+      <c r="A285" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  📊 Métricas derivadas (para modelo predictivo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="20" customHeight="1">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>Métrica calculada</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>Gimnasia y Esgrima</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="20" customHeight="1">
+      <c r="A287" s="20" t="inlineStr">
+        <is>
+          <t>Precisión de tiros - Local (%)</t>
+        </is>
+      </c>
+      <c r="B287" s="21" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="C287" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="20" customHeight="1">
+      <c r="A288" s="17" t="inlineStr">
+        <is>
+          <t>Precisión de tiros - Visitante (%)</t>
+        </is>
+      </c>
+      <c r="B288" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="C288" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="20" customHeight="1">
+      <c r="A289" s="20" t="inlineStr">
+        <is>
+          <t>xG por tiro - Local</t>
+        </is>
+      </c>
+      <c r="B289" s="21" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="C289" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="20" customHeight="1">
+      <c r="A290" s="17" t="inlineStr">
+        <is>
+          <t>xG por tiro - Visitante</t>
+        </is>
+      </c>
+      <c r="B290" s="18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C290" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="20" customHeight="1">
+      <c r="A291" s="20" t="inlineStr">
+        <is>
+          <t>Eficiencia oportunidades claras - Local (%)</t>
+        </is>
+      </c>
+      <c r="B291" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C291" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="20" customHeight="1">
+      <c r="A292" s="17" t="inlineStr">
+        <is>
+          <t>Eficiencia oportunidades claras - Visitante (%)</t>
+        </is>
+      </c>
+      <c r="B292" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C292" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="20" customHeight="1">
+      <c r="A293" s="20" t="inlineStr">
+        <is>
+          <t>% Regates exitosos - Local</t>
+        </is>
+      </c>
+      <c r="B293" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C293" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="20" customHeight="1">
+      <c r="A294" s="17" t="inlineStr">
+        <is>
+          <t>% Regates exitosos - Visitante</t>
+        </is>
+      </c>
+      <c r="B294" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C294" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="20" customHeight="1">
+      <c r="A295" s="20" t="inlineStr">
+        <is>
+          <t>% Duelos ganados - Local</t>
+        </is>
+      </c>
+      <c r="B295" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C295" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="20" customHeight="1">
+      <c r="A296" s="17" t="inlineStr">
+        <is>
+          <t>% Duelos ganados - Visitante</t>
+        </is>
+      </c>
+      <c r="B296" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C296" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="20" customHeight="1">
+      <c r="A297" s="20" t="inlineStr">
+        <is>
+          <t>Diferencial xG (Local - Visitante)</t>
+        </is>
+      </c>
+      <c r="B297" s="21" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="C297" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="20" customHeight="1">
+      <c r="A298" s="17" t="inlineStr">
+        <is>
+          <t>% Tiros dentro del área - Local</t>
+        </is>
+      </c>
+      <c r="B298" s="18" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="C298" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="20" customHeight="1">
+      <c r="A299" s="20" t="inlineStr">
+        <is>
+          <t>% Tiros dentro del área - Visitante</t>
+        </is>
+      </c>
+      <c r="B299" s="21" t="n">
+        <v>60</v>
+      </c>
+      <c r="C299" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="20" customHeight="1"/>
+    <row r="301" ht="20" customHeight="1"/>
+    <row r="302" ht="20" customHeight="1">
+      <c r="A302" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Instituto De Córdoba  vs  Club Atlético Platense</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="20" customHeight="1">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>Instituto De Córdoba</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>Club Atlético Platense</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="20" customHeight="1">
+      <c r="A304" s="14" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="B304" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C304" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305" ht="20" customHeight="1">
+      <c r="A305" s="15" t="inlineStr">
+        <is>
+          <t>Posesión de balón</t>
+        </is>
+      </c>
+      <c r="B305" s="16" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="C305" s="16" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="20" customHeight="1">
+      <c r="A306" s="17" t="inlineStr">
+        <is>
+          <t>Goles esperados (xG)</t>
+        </is>
+      </c>
+      <c r="B306" s="18" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="C306" s="18" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="20" customHeight="1">
+      <c r="A307" s="15" t="inlineStr">
+        <is>
+          <t>Tiros totales</t>
+        </is>
+      </c>
+      <c r="B307" s="16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C307" s="16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="20" customHeight="1">
+      <c r="A308" s="17" t="inlineStr">
+        <is>
+          <t>Tiros al arco</t>
+        </is>
+      </c>
+      <c r="B308" s="18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C308" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="20" customHeight="1">
+      <c r="A309" s="15" t="inlineStr">
+        <is>
+          <t>Tiros afuera</t>
+        </is>
+      </c>
+      <c r="B309" s="16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C309" s="16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="20" customHeight="1">
+      <c r="A310" s="17" t="inlineStr">
+        <is>
+          <t>Tiros bloqueados</t>
+        </is>
+      </c>
+      <c r="B310" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C310" s="18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="20" customHeight="1">
+      <c r="A311" s="15" t="inlineStr">
+        <is>
+          <t>Córners</t>
+        </is>
+      </c>
+      <c r="B311" s="16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C311" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="20" customHeight="1">
+      <c r="A312" s="17" t="inlineStr">
+        <is>
+          <t>Fueras de juego</t>
+        </is>
+      </c>
+      <c r="B312" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C312" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="20" customHeight="1">
+      <c r="A313" s="15" t="inlineStr">
+        <is>
+          <t>Faltas</t>
+        </is>
+      </c>
+      <c r="B313" s="16" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C313" s="16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="20" customHeight="1">
+      <c r="A314" s="17" t="inlineStr">
+        <is>
+          <t>Tarjetas amarillas</t>
+        </is>
+      </c>
+      <c r="B314" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C314" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="20" customHeight="1">
+      <c r="A315" s="15" t="inlineStr">
+        <is>
+          <t>Pases totales</t>
+        </is>
+      </c>
+      <c r="B315" s="16" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="C315" s="16" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="20" customHeight="1">
+      <c r="A316" s="17" t="inlineStr">
+        <is>
+          <t>Pases precisos</t>
+        </is>
+      </c>
+      <c r="B316" s="18" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="C316" s="18" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="20" customHeight="1">
+      <c r="A317" s="15" t="inlineStr">
+        <is>
+          <t>Atajadas del arquero</t>
+        </is>
+      </c>
+      <c r="B317" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C317" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="20" customHeight="1">
+      <c r="A318" s="17" t="inlineStr">
+        <is>
+          <t>Quites</t>
+        </is>
+      </c>
+      <c r="B318" s="18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C318" s="18" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="20" customHeight="1">
+      <c r="A319" s="15" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="B319" s="16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C319" s="16" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="20" customHeight="1">
+      <c r="A320" s="17" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="B320" s="18" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C320" s="18" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="20" customHeight="1">
+      <c r="A321" s="15" t="inlineStr">
+        <is>
+          <t>Ocasiones claras</t>
+        </is>
+      </c>
+      <c r="B321" s="16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C321" s="16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="20" customHeight="1">
+      <c r="A322" s="17" t="inlineStr">
+        <is>
+          <t>Ocasiones claras falladas</t>
+        </is>
+      </c>
+      <c r="B322" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C322" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="20" customHeight="1">
+      <c r="A323" s="15" t="inlineStr">
+        <is>
+          <t>Regates intentados</t>
+        </is>
+      </c>
+      <c r="B323" s="16" t="inlineStr">
+        <is>
+          <t>8/15 (53%)</t>
+        </is>
+      </c>
+      <c r="C323" s="16" t="inlineStr">
+        <is>
+          <t>14/18 (78%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="20" customHeight="1">
+      <c r="A324" s="17" t="inlineStr">
+        <is>
+          <t>Tiros dentro del área</t>
+        </is>
+      </c>
+      <c r="B324" s="18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C324" s="18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="20" customHeight="1">
+      <c r="A325" s="15" t="inlineStr">
+        <is>
+          <t>Tiros fuera del área</t>
+        </is>
+      </c>
+      <c r="B325" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C325" s="16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="20" customHeight="1">
+      <c r="A326" s="17" t="inlineStr">
+        <is>
+          <t>Goles evitados (arquero)</t>
+        </is>
+      </c>
+      <c r="B326" s="18" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="C326" s="18" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="20" customHeight="1"/>
+    <row r="328" ht="20" customHeight="1">
+      <c r="A328" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  📊 Métricas derivadas (para modelo predictivo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="329" ht="20" customHeight="1">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>Métrica calculada</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>Instituto De Córdoba</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>Club Atlético Platense</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" ht="20" customHeight="1">
+      <c r="A330" s="20" t="inlineStr">
+        <is>
+          <t>Precisión de tiros - Local (%)</t>
+        </is>
+      </c>
+      <c r="B330" s="21" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="C330" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="331" ht="20" customHeight="1">
+      <c r="A331" s="17" t="inlineStr">
+        <is>
+          <t>Precisión de tiros - Visitante (%)</t>
+        </is>
+      </c>
+      <c r="B331" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="C331" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="332" ht="20" customHeight="1">
+      <c r="A332" s="20" t="inlineStr">
+        <is>
+          <t>xG por tiro - Local</t>
+        </is>
+      </c>
+      <c r="B332" s="21" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="C332" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="333" ht="20" customHeight="1">
+      <c r="A333" s="17" t="inlineStr">
+        <is>
+          <t>xG por tiro - Visitante</t>
+        </is>
+      </c>
+      <c r="B333" s="18" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="C333" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="334" ht="20" customHeight="1">
+      <c r="A334" s="20" t="inlineStr">
+        <is>
+          <t>Eficiencia oportunidades claras - Local (%)</t>
+        </is>
+      </c>
+      <c r="B334" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C334" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="20" customHeight="1">
+      <c r="A335" s="17" t="inlineStr">
+        <is>
+          <t>Eficiencia oportunidades claras - Visitante (%)</t>
+        </is>
+      </c>
+      <c r="B335" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C335" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="20" customHeight="1">
+      <c r="A336" s="20" t="inlineStr">
+        <is>
+          <t>% Regates exitosos - Local</t>
+        </is>
+      </c>
+      <c r="B336" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C336" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="337" ht="20" customHeight="1">
+      <c r="A337" s="17" t="inlineStr">
+        <is>
+          <t>% Regates exitosos - Visitante</t>
+        </is>
+      </c>
+      <c r="B337" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C337" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="20" customHeight="1">
+      <c r="A338" s="20" t="inlineStr">
+        <is>
+          <t>% Duelos ganados - Local</t>
+        </is>
+      </c>
+      <c r="B338" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C338" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="339" ht="20" customHeight="1">
+      <c r="A339" s="17" t="inlineStr">
+        <is>
+          <t>% Duelos ganados - Visitante</t>
+        </is>
+      </c>
+      <c r="B339" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C339" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="340" ht="20" customHeight="1">
+      <c r="A340" s="20" t="inlineStr">
+        <is>
+          <t>Diferencial xG (Local - Visitante)</t>
+        </is>
+      </c>
+      <c r="B340" s="21" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="C340" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="341" ht="20" customHeight="1">
+      <c r="A341" s="17" t="inlineStr">
+        <is>
+          <t>% Tiros dentro del área - Local</t>
+        </is>
+      </c>
+      <c r="B341" s="18" t="n">
+        <v>75</v>
+      </c>
+      <c r="C341" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="342" ht="20" customHeight="1">
+      <c r="A342" s="20" t="inlineStr">
+        <is>
+          <t>% Tiros dentro del área - Visitante</t>
+        </is>
+      </c>
+      <c r="B342" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="C342" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="343" ht="20" customHeight="1"/>
+    <row r="344" ht="20" customHeight="1"/>
+    <row r="345" ht="20" customHeight="1">
+      <c r="A345" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CA Talleres  vs  Vélez Sarsfield</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="20" customHeight="1">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>CA Talleres</t>
+        </is>
+      </c>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>Vélez Sarsfield</t>
+        </is>
+      </c>
+    </row>
+    <row r="347" ht="20" customHeight="1">
+      <c r="A347" s="14" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="B347" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C347" s="14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="348" ht="20" customHeight="1">
+      <c r="A348" s="15" t="inlineStr">
+        <is>
+          <t>Posesión de balón</t>
+        </is>
+      </c>
+      <c r="B348" s="16" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="C348" s="16" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+    </row>
+    <row r="349" ht="20" customHeight="1">
+      <c r="A349" s="17" t="inlineStr">
+        <is>
+          <t>Goles esperados (xG)</t>
+        </is>
+      </c>
+      <c r="B349" s="18" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="C349" s="18" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="350" ht="20" customHeight="1">
+      <c r="A350" s="15" t="inlineStr">
+        <is>
+          <t>Tiros totales</t>
+        </is>
+      </c>
+      <c r="B350" s="16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C350" s="16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="351" ht="20" customHeight="1">
+      <c r="A351" s="17" t="inlineStr">
+        <is>
+          <t>Tiros al arco</t>
+        </is>
+      </c>
+      <c r="B351" s="18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C351" s="18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="352" ht="20" customHeight="1">
+      <c r="A352" s="15" t="inlineStr">
+        <is>
+          <t>Tiros afuera</t>
+        </is>
+      </c>
+      <c r="B352" s="16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C352" s="16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="353" ht="20" customHeight="1">
+      <c r="A353" s="17" t="inlineStr">
+        <is>
+          <t>Tiros bloqueados</t>
+        </is>
+      </c>
+      <c r="B353" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C353" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="354" ht="20" customHeight="1">
+      <c r="A354" s="15" t="inlineStr">
+        <is>
+          <t>Córners</t>
+        </is>
+      </c>
+      <c r="B354" s="16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C354" s="16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="355" ht="20" customHeight="1">
+      <c r="A355" s="17" t="inlineStr">
+        <is>
+          <t>Fueras de juego</t>
+        </is>
+      </c>
+      <c r="B355" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C355" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="356" ht="20" customHeight="1">
+      <c r="A356" s="15" t="inlineStr">
+        <is>
+          <t>Faltas</t>
+        </is>
+      </c>
+      <c r="B356" s="16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C356" s="16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="357" ht="20" customHeight="1">
+      <c r="A357" s="17" t="inlineStr">
+        <is>
+          <t>Tarjetas amarillas</t>
+        </is>
+      </c>
+      <c r="B357" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C357" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="358" ht="20" customHeight="1">
+      <c r="A358" s="15" t="inlineStr">
+        <is>
+          <t>Pases totales</t>
+        </is>
+      </c>
+      <c r="B358" s="16" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="C358" s="16" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+    </row>
+    <row r="359" ht="20" customHeight="1">
+      <c r="A359" s="17" t="inlineStr">
+        <is>
+          <t>Pases precisos</t>
+        </is>
+      </c>
+      <c r="B359" s="18" t="inlineStr">
+        <is>
+          <t>533</t>
+        </is>
+      </c>
+      <c r="C359" s="18" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+    </row>
+    <row r="360" ht="20" customHeight="1">
+      <c r="A360" s="15" t="inlineStr">
+        <is>
+          <t>Atajadas del arquero</t>
+        </is>
+      </c>
+      <c r="B360" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C360" s="16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="361" ht="20" customHeight="1">
+      <c r="A361" s="17" t="inlineStr">
+        <is>
+          <t>Quites</t>
+        </is>
+      </c>
+      <c r="B361" s="18" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C361" s="18" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="362" ht="20" customHeight="1">
+      <c r="A362" s="15" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="B362" s="16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C362" s="16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="363" ht="20" customHeight="1">
+      <c r="A363" s="17" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="B363" s="18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C363" s="18" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="364" ht="20" customHeight="1">
+      <c r="A364" s="15" t="inlineStr">
+        <is>
+          <t>Ocasiones claras</t>
+        </is>
+      </c>
+      <c r="B364" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C364" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="365" ht="20" customHeight="1">
+      <c r="A365" s="17" t="inlineStr">
+        <is>
+          <t>Ocasiones claras falladas</t>
+        </is>
+      </c>
+      <c r="B365" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C365" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="366" ht="20" customHeight="1">
+      <c r="A366" s="15" t="inlineStr">
+        <is>
+          <t>Regates intentados</t>
+        </is>
+      </c>
+      <c r="B366" s="16" t="inlineStr">
+        <is>
+          <t>16/25 (64%)</t>
+        </is>
+      </c>
+      <c r="C366" s="16" t="inlineStr">
+        <is>
+          <t>4/12 (33%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="367" ht="20" customHeight="1">
+      <c r="A367" s="17" t="inlineStr">
+        <is>
+          <t>Tiros dentro del área</t>
+        </is>
+      </c>
+      <c r="B367" s="18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C367" s="18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="368" ht="20" customHeight="1">
+      <c r="A368" s="15" t="inlineStr">
+        <is>
+          <t>Tiros fuera del área</t>
+        </is>
+      </c>
+      <c r="B368" s="16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C368" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="369" ht="20" customHeight="1">
+      <c r="A369" s="17" t="inlineStr">
+        <is>
+          <t>Goles evitados (arquero)</t>
+        </is>
+      </c>
+      <c r="B369" s="18" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="C369" s="18" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="370" ht="20" customHeight="1"/>
+    <row r="371" ht="20" customHeight="1">
+      <c r="A371" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  📊 Métricas derivadas (para modelo predictivo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="372" ht="20" customHeight="1">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>Métrica calculada</t>
+        </is>
+      </c>
+      <c r="B372" s="2" t="inlineStr">
+        <is>
+          <t>CA Talleres</t>
+        </is>
+      </c>
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>Vélez Sarsfield</t>
+        </is>
+      </c>
+    </row>
+    <row r="373" ht="20" customHeight="1">
+      <c r="A373" s="20" t="inlineStr">
+        <is>
+          <t>Precisión de tiros - Local (%)</t>
+        </is>
+      </c>
+      <c r="B373" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="C373" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="374" ht="20" customHeight="1">
+      <c r="A374" s="17" t="inlineStr">
+        <is>
+          <t>Precisión de tiros - Visitante (%)</t>
+        </is>
+      </c>
+      <c r="B374" s="18" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="C374" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="375" ht="20" customHeight="1">
+      <c r="A375" s="20" t="inlineStr">
+        <is>
+          <t>xG por tiro - Local</t>
+        </is>
+      </c>
+      <c r="B375" s="21" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="C375" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="376" ht="20" customHeight="1">
+      <c r="A376" s="17" t="inlineStr">
+        <is>
+          <t>xG por tiro - Visitante</t>
+        </is>
+      </c>
+      <c r="B376" s="18" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="C376" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="377" ht="20" customHeight="1">
+      <c r="A377" s="20" t="inlineStr">
+        <is>
+          <t>Eficiencia oportunidades claras - Local (%)</t>
+        </is>
+      </c>
+      <c r="B377" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C377" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="378" ht="20" customHeight="1">
+      <c r="A378" s="17" t="inlineStr">
+        <is>
+          <t>Eficiencia oportunidades claras - Visitante (%)</t>
+        </is>
+      </c>
+      <c r="B378" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C378" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="379" ht="20" customHeight="1">
+      <c r="A379" s="20" t="inlineStr">
+        <is>
+          <t>% Regates exitosos - Local</t>
+        </is>
+      </c>
+      <c r="B379" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C379" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="380" ht="20" customHeight="1">
+      <c r="A380" s="17" t="inlineStr">
+        <is>
+          <t>% Regates exitosos - Visitante</t>
+        </is>
+      </c>
+      <c r="B380" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C380" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="381" ht="20" customHeight="1">
+      <c r="A381" s="20" t="inlineStr">
+        <is>
+          <t>% Duelos ganados - Local</t>
+        </is>
+      </c>
+      <c r="B381" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C381" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="382" ht="20" customHeight="1">
+      <c r="A382" s="17" t="inlineStr">
+        <is>
+          <t>% Duelos ganados - Visitante</t>
+        </is>
+      </c>
+      <c r="B382" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C382" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="383" ht="20" customHeight="1">
+      <c r="A383" s="20" t="inlineStr">
+        <is>
+          <t>Diferencial xG (Local - Visitante)</t>
+        </is>
+      </c>
+      <c r="B383" s="21" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="C383" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="384" ht="20" customHeight="1">
+      <c r="A384" s="17" t="inlineStr">
+        <is>
+          <t>% Tiros dentro del área - Local</t>
+        </is>
+      </c>
+      <c r="B384" s="18" t="n">
+        <v>50</v>
+      </c>
+      <c r="C384" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="385" ht="20" customHeight="1">
+      <c r="A385" s="20" t="inlineStr">
+        <is>
+          <t>% Tiros dentro del área - Visitante</t>
+        </is>
+      </c>
+      <c r="B385" s="21" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="C385" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="386" ht="20" customHeight="1"/>
+    <row r="387" ht="20" customHeight="1"/>
+    <row r="388" ht="20" customHeight="1">
+      <c r="A388" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Independiente Rivadavia  vs  Huracán</t>
+        </is>
+      </c>
+    </row>
+    <row r="389" ht="20" customHeight="1">
+      <c r="A389" s="2" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B389" s="2" t="inlineStr">
+        <is>
+          <t>Independiente Rivadavia</t>
+        </is>
+      </c>
+      <c r="C389" s="2" t="inlineStr">
+        <is>
+          <t>Huracán</t>
+        </is>
+      </c>
+    </row>
+    <row r="390" ht="20" customHeight="1">
+      <c r="A390" s="14" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="B390" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C390" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="391" ht="20" customHeight="1">
+      <c r="A391" s="15" t="inlineStr">
+        <is>
+          <t>Posesión de balón</t>
+        </is>
+      </c>
+      <c r="B391" s="16" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="C391" s="16" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+    </row>
+    <row r="392" ht="20" customHeight="1">
+      <c r="A392" s="17" t="inlineStr">
+        <is>
+          <t>Goles esperados (xG)</t>
+        </is>
+      </c>
+      <c r="B392" s="18" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="C392" s="18" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="393" ht="20" customHeight="1">
+      <c r="A393" s="15" t="inlineStr">
+        <is>
+          <t>Tiros totales</t>
+        </is>
+      </c>
+      <c r="B393" s="16" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C393" s="16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="394" ht="20" customHeight="1">
+      <c r="A394" s="17" t="inlineStr">
+        <is>
+          <t>Tiros al arco</t>
+        </is>
+      </c>
+      <c r="B394" s="18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C394" s="18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="395" ht="20" customHeight="1">
+      <c r="A395" s="15" t="inlineStr">
+        <is>
+          <t>Tiros afuera</t>
+        </is>
+      </c>
+      <c r="B395" s="16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C395" s="16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="396" ht="20" customHeight="1">
+      <c r="A396" s="17" t="inlineStr">
+        <is>
+          <t>Tiros bloqueados</t>
+        </is>
+      </c>
+      <c r="B396" s="18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C396" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="397" ht="20" customHeight="1">
+      <c r="A397" s="15" t="inlineStr">
+        <is>
+          <t>Córners</t>
+        </is>
+      </c>
+      <c r="B397" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C397" s="16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="398" ht="20" customHeight="1">
+      <c r="A398" s="17" t="inlineStr">
+        <is>
+          <t>Fueras de juego</t>
+        </is>
+      </c>
+      <c r="B398" s="18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C398" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="399" ht="20" customHeight="1">
+      <c r="A399" s="15" t="inlineStr">
+        <is>
+          <t>Faltas</t>
+        </is>
+      </c>
+      <c r="B399" s="16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C399" s="16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="400" ht="20" customHeight="1">
+      <c r="A400" s="17" t="inlineStr">
+        <is>
+          <t>Tarjetas rojas</t>
+        </is>
+      </c>
+      <c r="B400" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C400" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="401" ht="20" customHeight="1">
+      <c r="A401" s="15" t="inlineStr">
+        <is>
+          <t>Pases totales</t>
+        </is>
+      </c>
+      <c r="B401" s="16" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="C401" s="16" t="inlineStr">
+        <is>
+          <t>481</t>
+        </is>
+      </c>
+    </row>
+    <row r="402" ht="20" customHeight="1">
+      <c r="A402" s="17" t="inlineStr">
+        <is>
+          <t>Pases precisos</t>
+        </is>
+      </c>
+      <c r="B402" s="18" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="C402" s="18" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+    </row>
+    <row r="403" ht="20" customHeight="1">
+      <c r="A403" s="15" t="inlineStr">
+        <is>
+          <t>Atajadas del arquero</t>
+        </is>
+      </c>
+      <c r="B403" s="16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C403" s="16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="404" ht="20" customHeight="1">
+      <c r="A404" s="17" t="inlineStr">
+        <is>
+          <t>Quites</t>
+        </is>
+      </c>
+      <c r="B404" s="18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C404" s="18" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="405" ht="20" customHeight="1">
+      <c r="A405" s="15" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="B405" s="16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C405" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="406" ht="20" customHeight="1">
+      <c r="A406" s="17" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="B406" s="18" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C406" s="18" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
+    <row r="407" ht="20" customHeight="1">
+      <c r="A407" s="15" t="inlineStr">
+        <is>
+          <t>Ocasiones claras</t>
+        </is>
+      </c>
+      <c r="B407" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C407" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="408" ht="20" customHeight="1">
+      <c r="A408" s="17" t="inlineStr">
+        <is>
+          <t>Ocasiones claras falladas</t>
+        </is>
+      </c>
+      <c r="B408" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C408" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="409" ht="20" customHeight="1">
+      <c r="A409" s="15" t="inlineStr">
+        <is>
+          <t>Regates intentados</t>
+        </is>
+      </c>
+      <c r="B409" s="16" t="inlineStr">
+        <is>
+          <t>10/18 (56%)</t>
+        </is>
+      </c>
+      <c r="C409" s="16" t="inlineStr">
+        <is>
+          <t>5/12 (42%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="410" ht="20" customHeight="1">
+      <c r="A410" s="17" t="inlineStr">
+        <is>
+          <t>Tiros dentro del área</t>
+        </is>
+      </c>
+      <c r="B410" s="18" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C410" s="18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="411" ht="20" customHeight="1">
+      <c r="A411" s="15" t="inlineStr">
+        <is>
+          <t>Tiros fuera del área</t>
+        </is>
+      </c>
+      <c r="B411" s="16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C411" s="16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="412" ht="20" customHeight="1">
+      <c r="A412" s="17" t="inlineStr">
+        <is>
+          <t>Goles evitados (arquero)</t>
+        </is>
+      </c>
+      <c r="B412" s="18" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="C412" s="18" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="413" ht="20" customHeight="1"/>
+    <row r="414" ht="20" customHeight="1">
+      <c r="A414" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  📊 Métricas derivadas (para modelo predictivo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="415" ht="20" customHeight="1">
+      <c r="A415" s="2" t="inlineStr">
+        <is>
+          <t>Métrica calculada</t>
+        </is>
+      </c>
+      <c r="B415" s="2" t="inlineStr">
+        <is>
+          <t>Independiente Rivadavia</t>
+        </is>
+      </c>
+      <c r="C415" s="2" t="inlineStr">
+        <is>
+          <t>Huracán</t>
+        </is>
+      </c>
+    </row>
+    <row r="416" ht="20" customHeight="1">
+      <c r="A416" s="20" t="inlineStr">
+        <is>
+          <t>Precisión de tiros - Local (%)</t>
+        </is>
+      </c>
+      <c r="B416" s="21" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="C416" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="417" ht="20" customHeight="1">
+      <c r="A417" s="17" t="inlineStr">
+        <is>
+          <t>Precisión de tiros - Visitante (%)</t>
+        </is>
+      </c>
+      <c r="B417" s="18" t="n">
+        <v>50</v>
+      </c>
+      <c r="C417" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="418" ht="20" customHeight="1">
+      <c r="A418" s="20" t="inlineStr">
+        <is>
+          <t>xG por tiro - Local</t>
+        </is>
+      </c>
+      <c r="B418" s="21" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="C418" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="419" ht="20" customHeight="1">
+      <c r="A419" s="17" t="inlineStr">
+        <is>
+          <t>xG por tiro - Visitante</t>
+        </is>
+      </c>
+      <c r="B419" s="18" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="C419" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="420" ht="20" customHeight="1">
+      <c r="A420" s="20" t="inlineStr">
+        <is>
+          <t>Eficiencia oportunidades claras - Local (%)</t>
+        </is>
+      </c>
+      <c r="B420" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C420" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="421" ht="20" customHeight="1">
+      <c r="A421" s="17" t="inlineStr">
+        <is>
+          <t>Eficiencia oportunidades claras - Visitante (%)</t>
+        </is>
+      </c>
+      <c r="B421" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C421" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="422" ht="20" customHeight="1">
+      <c r="A422" s="20" t="inlineStr">
+        <is>
+          <t>% Regates exitosos - Local</t>
+        </is>
+      </c>
+      <c r="B422" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C422" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="423" ht="20" customHeight="1">
+      <c r="A423" s="17" t="inlineStr">
+        <is>
+          <t>% Regates exitosos - Visitante</t>
+        </is>
+      </c>
+      <c r="B423" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C423" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="424" ht="20" customHeight="1">
+      <c r="A424" s="20" t="inlineStr">
+        <is>
+          <t>% Duelos ganados - Local</t>
+        </is>
+      </c>
+      <c r="B424" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C424" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="425" ht="20" customHeight="1">
+      <c r="A425" s="17" t="inlineStr">
+        <is>
+          <t>% Duelos ganados - Visitante</t>
+        </is>
+      </c>
+      <c r="B425" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C425" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="426" ht="20" customHeight="1">
+      <c r="A426" s="20" t="inlineStr">
+        <is>
+          <t>Diferencial xG (Local - Visitante)</t>
+        </is>
+      </c>
+      <c r="B426" s="21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="C426" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="427" ht="20" customHeight="1">
+      <c r="A427" s="17" t="inlineStr">
+        <is>
+          <t>% Tiros dentro del área - Local</t>
+        </is>
+      </c>
+      <c r="B427" s="18" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="C427" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="428" ht="20" customHeight="1">
+      <c r="A428" s="20" t="inlineStr">
+        <is>
+          <t>% Tiros dentro del área - Visitante</t>
+        </is>
+      </c>
+      <c r="B428" s="21" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="C428" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="429" ht="20" customHeight="1"/>
+    <row r="430" ht="20" customHeight="1"/>
+    <row r="431" ht="20" customHeight="1">
+      <c r="A431" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CA Independiente  vs  Newell's Old Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="432" ht="20" customHeight="1">
+      <c r="A432" s="2" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B432" s="2" t="inlineStr">
+        <is>
+          <t>CA Independiente</t>
+        </is>
+      </c>
+      <c r="C432" s="2" t="inlineStr">
+        <is>
+          <t>Newell's Old Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="433" ht="20" customHeight="1">
+      <c r="A433" s="14" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="B433" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C433" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434" ht="20" customHeight="1">
+      <c r="A434" s="15" t="inlineStr">
+        <is>
+          <t>Posesión de balón</t>
+        </is>
+      </c>
+      <c r="B434" s="16" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="C434" s="16" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+    </row>
+    <row r="435" ht="20" customHeight="1">
+      <c r="A435" s="17" t="inlineStr">
+        <is>
+          <t>Goles esperados (xG)</t>
+        </is>
+      </c>
+      <c r="B435" s="18" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="C435" s="18" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="436" ht="20" customHeight="1">
+      <c r="A436" s="15" t="inlineStr">
+        <is>
+          <t>Tiros totales</t>
+        </is>
+      </c>
+      <c r="B436" s="16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C436" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="437" ht="20" customHeight="1">
+      <c r="A437" s="17" t="inlineStr">
+        <is>
+          <t>Tiros al arco</t>
+        </is>
+      </c>
+      <c r="B437" s="18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C437" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="438" ht="20" customHeight="1">
+      <c r="A438" s="15" t="inlineStr">
+        <is>
+          <t>Tiros afuera</t>
+        </is>
+      </c>
+      <c r="B438" s="16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C438" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="439" ht="20" customHeight="1">
+      <c r="A439" s="17" t="inlineStr">
+        <is>
+          <t>Tiros bloqueados</t>
+        </is>
+      </c>
+      <c r="B439" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C439" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="440" ht="20" customHeight="1">
+      <c r="A440" s="15" t="inlineStr">
+        <is>
+          <t>Córners</t>
+        </is>
+      </c>
+      <c r="B440" s="16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C440" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="441" ht="20" customHeight="1">
+      <c r="A441" s="17" t="inlineStr">
+        <is>
+          <t>Fueras de juego</t>
+        </is>
+      </c>
+      <c r="B441" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C441" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="442" ht="20" customHeight="1">
+      <c r="A442" s="15" t="inlineStr">
+        <is>
+          <t>Faltas</t>
+        </is>
+      </c>
+      <c r="B442" s="16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C442" s="16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="443" ht="20" customHeight="1">
+      <c r="A443" s="17" t="inlineStr">
+        <is>
+          <t>Tarjetas amarillas</t>
+        </is>
+      </c>
+      <c r="B443" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C443" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="444" ht="20" customHeight="1">
+      <c r="A444" s="15" t="inlineStr">
+        <is>
+          <t>Pases totales</t>
+        </is>
+      </c>
+      <c r="B444" s="16" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="C444" s="16" t="inlineStr">
+        <is>
+          <t>449</t>
+        </is>
+      </c>
+    </row>
+    <row r="445" ht="20" customHeight="1">
+      <c r="A445" s="17" t="inlineStr">
+        <is>
+          <t>Pases precisos</t>
+        </is>
+      </c>
+      <c r="B445" s="18" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="C445" s="18" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+    </row>
+    <row r="446" ht="20" customHeight="1">
+      <c r="A446" s="15" t="inlineStr">
+        <is>
+          <t>Atajadas del arquero</t>
+        </is>
+      </c>
+      <c r="B446" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C446" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="447" ht="20" customHeight="1">
+      <c r="A447" s="17" t="inlineStr">
+        <is>
+          <t>Quites</t>
+        </is>
+      </c>
+      <c r="B447" s="18" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C447" s="18" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="448" ht="20" customHeight="1">
+      <c r="A448" s="15" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="B448" s="16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C448" s="16" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="449" ht="20" customHeight="1">
+      <c r="A449" s="17" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="B449" s="18" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C449" s="18" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="450" ht="20" customHeight="1">
+      <c r="A450" s="15" t="inlineStr">
+        <is>
+          <t>Ocasiones claras</t>
+        </is>
+      </c>
+      <c r="B450" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C450" s="16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="451" ht="20" customHeight="1">
+      <c r="A451" s="17" t="inlineStr">
+        <is>
+          <t>Ocasiones claras falladas</t>
+        </is>
+      </c>
+      <c r="B451" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C451" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="452" ht="20" customHeight="1">
+      <c r="A452" s="15" t="inlineStr">
+        <is>
+          <t>Regates intentados</t>
+        </is>
+      </c>
+      <c r="B452" s="16" t="inlineStr">
+        <is>
+          <t>15/28 (54%)</t>
+        </is>
+      </c>
+      <c r="C452" s="16" t="inlineStr">
+        <is>
+          <t>9/29 (31%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="453" ht="20" customHeight="1">
+      <c r="A453" s="17" t="inlineStr">
+        <is>
+          <t>Tiros dentro del área</t>
+        </is>
+      </c>
+      <c r="B453" s="18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C453" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="454" ht="20" customHeight="1">
+      <c r="A454" s="15" t="inlineStr">
+        <is>
+          <t>Tiros fuera del área</t>
+        </is>
+      </c>
+      <c r="B454" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C454" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="455" ht="20" customHeight="1">
+      <c r="A455" s="17" t="inlineStr">
+        <is>
+          <t>Goles evitados (arquero)</t>
+        </is>
+      </c>
+      <c r="B455" s="18" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="C455" s="18" t="inlineStr">
+        <is>
+          <t>-0.09</t>
+        </is>
+      </c>
+    </row>
+    <row r="456" ht="20" customHeight="1"/>
+    <row r="457" ht="20" customHeight="1">
+      <c r="A457" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  📊 Métricas derivadas (para modelo predictivo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="458" ht="20" customHeight="1">
+      <c r="A458" s="2" t="inlineStr">
+        <is>
+          <t>Métrica calculada</t>
+        </is>
+      </c>
+      <c r="B458" s="2" t="inlineStr">
+        <is>
+          <t>CA Independiente</t>
+        </is>
+      </c>
+      <c r="C458" s="2" t="inlineStr">
+        <is>
+          <t>Newell's Old Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="459" ht="20" customHeight="1">
+      <c r="A459" s="20" t="inlineStr">
+        <is>
+          <t>Precisión de tiros - Local (%)</t>
+        </is>
+      </c>
+      <c r="B459" s="21" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="C459" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="460" ht="20" customHeight="1">
+      <c r="A460" s="17" t="inlineStr">
+        <is>
+          <t>Precisión de tiros - Visitante (%)</t>
+        </is>
+      </c>
+      <c r="B460" s="18" t="n">
+        <v>50</v>
+      </c>
+      <c r="C460" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="461" ht="20" customHeight="1">
+      <c r="A461" s="20" t="inlineStr">
+        <is>
+          <t>xG por tiro - Local</t>
+        </is>
+      </c>
+      <c r="B461" s="21" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="C461" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="462" ht="20" customHeight="1">
+      <c r="A462" s="17" t="inlineStr">
+        <is>
+          <t>xG por tiro - Visitante</t>
+        </is>
+      </c>
+      <c r="B462" s="18" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="C462" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="463" ht="20" customHeight="1">
+      <c r="A463" s="20" t="inlineStr">
+        <is>
+          <t>Eficiencia oportunidades claras - Local (%)</t>
+        </is>
+      </c>
+      <c r="B463" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C463" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="464" ht="20" customHeight="1">
+      <c r="A464" s="17" t="inlineStr">
+        <is>
+          <t>Eficiencia oportunidades claras - Visitante (%)</t>
+        </is>
+      </c>
+      <c r="B464" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C464" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="465" ht="20" customHeight="1">
+      <c r="A465" s="20" t="inlineStr">
+        <is>
+          <t>% Regates exitosos - Local</t>
+        </is>
+      </c>
+      <c r="B465" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C465" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="466" ht="20" customHeight="1">
+      <c r="A466" s="17" t="inlineStr">
+        <is>
+          <t>% Regates exitosos - Visitante</t>
+        </is>
+      </c>
+      <c r="B466" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C466" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="467" ht="20" customHeight="1">
+      <c r="A467" s="20" t="inlineStr">
+        <is>
+          <t>% Duelos ganados - Local</t>
+        </is>
+      </c>
+      <c r="B467" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C467" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="468" ht="20" customHeight="1">
+      <c r="A468" s="17" t="inlineStr">
+        <is>
+          <t>% Duelos ganados - Visitante</t>
+        </is>
+      </c>
+      <c r="B468" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C468" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="469" ht="20" customHeight="1">
+      <c r="A469" s="20" t="inlineStr">
+        <is>
+          <t>Diferencial xG (Local - Visitante)</t>
+        </is>
+      </c>
+      <c r="B469" s="21" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="C469" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="470" ht="20" customHeight="1">
+      <c r="A470" s="17" t="inlineStr">
+        <is>
+          <t>% Tiros dentro del área - Local</t>
+        </is>
+      </c>
+      <c r="B470" s="18" t="n">
+        <v>75</v>
+      </c>
+      <c r="C470" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="471" ht="20" customHeight="1">
+      <c r="A471" s="20" t="inlineStr">
+        <is>
+          <t>% Tiros dentro del área - Visitante</t>
+        </is>
+      </c>
+      <c r="B471" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="C471" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="472" ht="20" customHeight="1"/>
+    <row r="473" ht="20" customHeight="1"/>
+    <row r="474" ht="20" customHeight="1">
+      <c r="A474" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Central Córdoba  vs  Atlético Tucumán</t>
+        </is>
+      </c>
+    </row>
+    <row r="475" ht="20" customHeight="1">
+      <c r="A475" s="2" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B475" s="2" t="inlineStr">
+        <is>
+          <t>Central Córdoba</t>
+        </is>
+      </c>
+      <c r="C475" s="2" t="inlineStr">
+        <is>
+          <t>Atlético Tucumán</t>
+        </is>
+      </c>
+    </row>
+    <row r="476" ht="20" customHeight="1">
+      <c r="A476" s="14" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="B476" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C476" s="14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="477" ht="20" customHeight="1">
+      <c r="A477" s="15" t="inlineStr">
+        <is>
+          <t>Posesión de balón</t>
+        </is>
+      </c>
+      <c r="B477" s="16" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="C477" s="16" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+    </row>
+    <row r="478" ht="20" customHeight="1">
+      <c r="A478" s="17" t="inlineStr">
+        <is>
+          <t>Goles esperados (xG)</t>
+        </is>
+      </c>
+      <c r="B478" s="18" t="inlineStr">
+        <is>
+          <t>0.41</t>
+        </is>
+      </c>
+      <c r="C478" s="18" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="479" ht="20" customHeight="1">
+      <c r="A479" s="15" t="inlineStr">
+        <is>
+          <t>Tiros totales</t>
+        </is>
+      </c>
+      <c r="B479" s="16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C479" s="16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="480" ht="20" customHeight="1">
+      <c r="A480" s="17" t="inlineStr">
+        <is>
+          <t>Tiros al arco</t>
+        </is>
+      </c>
+      <c r="B480" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C480" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="481" ht="20" customHeight="1">
+      <c r="A481" s="15" t="inlineStr">
+        <is>
+          <t>Tiros afuera</t>
+        </is>
+      </c>
+      <c r="B481" s="16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C481" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="482" ht="20" customHeight="1">
+      <c r="A482" s="17" t="inlineStr">
+        <is>
+          <t>Tiros bloqueados</t>
+        </is>
+      </c>
+      <c r="B482" s="18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C482" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="483" ht="20" customHeight="1">
+      <c r="A483" s="15" t="inlineStr">
+        <is>
+          <t>Córners</t>
+        </is>
+      </c>
+      <c r="B483" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C483" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="484" ht="20" customHeight="1">
+      <c r="A484" s="17" t="inlineStr">
+        <is>
+          <t>Fueras de juego</t>
+        </is>
+      </c>
+      <c r="B484" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C484" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="485" ht="20" customHeight="1">
+      <c r="A485" s="15" t="inlineStr">
+        <is>
+          <t>Faltas</t>
+        </is>
+      </c>
+      <c r="B485" s="16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C485" s="16" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="486" ht="20" customHeight="1">
+      <c r="A486" s="17" t="inlineStr">
+        <is>
+          <t>Tarjetas amarillas</t>
+        </is>
+      </c>
+      <c r="B486" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C486" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="487" ht="20" customHeight="1">
+      <c r="A487" s="15" t="inlineStr">
+        <is>
+          <t>Pases totales</t>
+        </is>
+      </c>
+      <c r="B487" s="16" t="inlineStr">
+        <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="C487" s="16" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+    </row>
+    <row r="488" ht="20" customHeight="1">
+      <c r="A488" s="17" t="inlineStr">
+        <is>
+          <t>Pases precisos</t>
+        </is>
+      </c>
+      <c r="B488" s="18" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="C488" s="18" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+    </row>
+    <row r="489" ht="20" customHeight="1">
+      <c r="A489" s="15" t="inlineStr">
+        <is>
+          <t>Atajadas del arquero</t>
+        </is>
+      </c>
+      <c r="B489" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C489" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="490" ht="20" customHeight="1">
+      <c r="A490" s="17" t="inlineStr">
+        <is>
+          <t>Quites</t>
+        </is>
+      </c>
+      <c r="B490" s="18" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C490" s="18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="491" ht="20" customHeight="1">
+      <c r="A491" s="15" t="inlineStr">
+        <is>
+          <t>Intercepciones</t>
+        </is>
+      </c>
+      <c r="B491" s="16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C491" s="16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="492" ht="20" customHeight="1">
+      <c r="A492" s="17" t="inlineStr">
+        <is>
+          <t>Despejes</t>
+        </is>
+      </c>
+      <c r="B492" s="18" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C492" s="18" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="493" ht="20" customHeight="1">
+      <c r="A493" s="15" t="inlineStr">
+        <is>
+          <t>Ocasiones claras</t>
+        </is>
+      </c>
+      <c r="B493" s="16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C493" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="494" ht="20" customHeight="1">
+      <c r="A494" s="17" t="inlineStr">
+        <is>
+          <t>Ocasiones claras falladas</t>
+        </is>
+      </c>
+      <c r="B494" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C494" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="495" ht="20" customHeight="1">
+      <c r="A495" s="15" t="inlineStr">
+        <is>
+          <t>Regates intentados</t>
+        </is>
+      </c>
+      <c r="B495" s="16" t="inlineStr">
+        <is>
+          <t>5/13 (38%)</t>
+        </is>
+      </c>
+      <c r="C495" s="16" t="inlineStr">
+        <is>
+          <t>7/17 (41%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="496" ht="20" customHeight="1">
+      <c r="A496" s="17" t="inlineStr">
+        <is>
+          <t>Tiros dentro del área</t>
+        </is>
+      </c>
+      <c r="B496" s="18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C496" s="18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="497" ht="20" customHeight="1">
+      <c r="A497" s="15" t="inlineStr">
+        <is>
+          <t>Tiros fuera del área</t>
+        </is>
+      </c>
+      <c r="B497" s="16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C497" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="498" ht="20" customHeight="1">
+      <c r="A498" s="17" t="inlineStr">
+        <is>
+          <t>Goles evitados (arquero)</t>
+        </is>
+      </c>
+      <c r="B498" s="18" t="inlineStr">
+        <is>
+          <t>-1.08</t>
+        </is>
+      </c>
+      <c r="C498" s="18" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="499" ht="20" customHeight="1"/>
+    <row r="500" ht="20" customHeight="1">
+      <c r="A500" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  📊 Métricas derivadas (para modelo predictivo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="501" ht="20" customHeight="1">
+      <c r="A501" s="2" t="inlineStr">
+        <is>
+          <t>Métrica calculada</t>
+        </is>
+      </c>
+      <c r="B501" s="2" t="inlineStr">
+        <is>
+          <t>Central Córdoba</t>
+        </is>
+      </c>
+      <c r="C501" s="2" t="inlineStr">
+        <is>
+          <t>Atlético Tucumán</t>
+        </is>
+      </c>
+    </row>
+    <row r="502" ht="20" customHeight="1">
+      <c r="A502" s="20" t="inlineStr">
+        <is>
+          <t>Precisión de tiros - Local (%)</t>
+        </is>
+      </c>
+      <c r="B502" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="C502" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="503" ht="20" customHeight="1">
+      <c r="A503" s="17" t="inlineStr">
+        <is>
+          <t>Precisión de tiros - Visitante (%)</t>
+        </is>
+      </c>
+      <c r="B503" s="18" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="C503" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="504" ht="20" customHeight="1">
+      <c r="A504" s="20" t="inlineStr">
+        <is>
+          <t>xG por tiro - Local</t>
+        </is>
+      </c>
+      <c r="B504" s="21" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="C504" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="505" ht="20" customHeight="1">
+      <c r="A505" s="17" t="inlineStr">
+        <is>
+          <t>xG por tiro - Visitante</t>
+        </is>
+      </c>
+      <c r="B505" s="18" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="C505" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="506" ht="20" customHeight="1">
+      <c r="A506" s="20" t="inlineStr">
+        <is>
+          <t>Eficiencia oportunidades claras - Local (%)</t>
+        </is>
+      </c>
+      <c r="B506" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C506" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="507" ht="20" customHeight="1">
+      <c r="A507" s="17" t="inlineStr">
+        <is>
+          <t>Eficiencia oportunidades claras - Visitante (%)</t>
+        </is>
+      </c>
+      <c r="B507" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C507" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="508" ht="20" customHeight="1">
+      <c r="A508" s="20" t="inlineStr">
+        <is>
+          <t>% Regates exitosos - Local</t>
+        </is>
+      </c>
+      <c r="B508" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C508" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="509" ht="20" customHeight="1">
+      <c r="A509" s="17" t="inlineStr">
+        <is>
+          <t>% Regates exitosos - Visitante</t>
+        </is>
+      </c>
+      <c r="B509" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C509" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="510" ht="20" customHeight="1">
+      <c r="A510" s="20" t="inlineStr">
+        <is>
+          <t>% Duelos ganados - Local</t>
+        </is>
+      </c>
+      <c r="B510" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C510" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="511" ht="20" customHeight="1">
+      <c r="A511" s="17" t="inlineStr">
+        <is>
+          <t>% Duelos ganados - Visitante</t>
+        </is>
+      </c>
+      <c r="B511" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C511" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="512" ht="20" customHeight="1">
+      <c r="A512" s="20" t="inlineStr">
+        <is>
+          <t>Diferencial xG (Local - Visitante)</t>
+        </is>
+      </c>
+      <c r="B512" s="21" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="C512" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="513" ht="20" customHeight="1">
+      <c r="A513" s="17" t="inlineStr">
+        <is>
+          <t>% Tiros dentro del área - Local</t>
+        </is>
+      </c>
+      <c r="B513" s="18" t="n">
+        <v>50</v>
+      </c>
+      <c r="C513" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="514" ht="20" customHeight="1">
+      <c r="A514" s="20" t="inlineStr">
+        <is>
+          <t>% Tiros dentro del área - Visitante</t>
+        </is>
+      </c>
+      <c r="B514" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="C514" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="A388:C388"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A474:C474"/>
+    <mergeCell ref="A285:C285"/>
+    <mergeCell ref="A113:C113"/>
+    <mergeCell ref="A242:C242"/>
+    <mergeCell ref="A302:C302"/>
+    <mergeCell ref="A414:C414"/>
+    <mergeCell ref="A259:C259"/>
+    <mergeCell ref="A371:C371"/>
+    <mergeCell ref="A156:C156"/>
+    <mergeCell ref="A199:C199"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A500:C500"/>
+    <mergeCell ref="A173:C173"/>
+    <mergeCell ref="A130:C130"/>
+    <mergeCell ref="A328:C328"/>
+    <mergeCell ref="A431:C431"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A216:C216"/>
+    <mergeCell ref="A70:C70"/>
+    <mergeCell ref="A457:C457"/>
+    <mergeCell ref="A87:C87"/>
+    <mergeCell ref="A345:C345"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/actual/clausura26.xlsx
+++ b/data/actual/clausura26.xlsx
@@ -3,17 +3,18 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DEB1AE75-4080-49F4-B117-4617AC82DCCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D10C262-495C-47FC-8526-98AB32A7D115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Fecha 1" sheetId="2" r:id="rId1"/>
-    <sheet name="Fecha 2" sheetId="1" r:id="rId2"/>
+    <sheet name="Fecha 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Fecha 2" sheetId="2" r:id="rId2"/>
     <sheet name="Fecha 3" sheetId="3" r:id="rId3"/>
     <sheet name="Fecha 4" sheetId="4" r:id="rId4"/>
     <sheet name="Fecha 5" sheetId="5" r:id="rId5"/>
     <sheet name="Fecha 6" sheetId="6" r:id="rId6"/>
+    <sheet name="Fecha 7" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9366" uniqueCount="893">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10917" uniqueCount="967">
   <si>
     <t xml:space="preserve">  Club Atlético Belgrano  vs  Rosario Central</t>
   </si>
@@ -2715,6 +2716,228 @@
   </si>
   <si>
     <t>3.47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Club Atlético Unión de Santa Fe  vs  Sarmiento</t>
+  </si>
+  <si>
+    <t>245</t>
+  </si>
+  <si>
+    <t>3/16 (19%)</t>
+  </si>
+  <si>
+    <t>-2.60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Boca Juniors  vs  CA Lanús</t>
+  </si>
+  <si>
+    <t>538</t>
+  </si>
+  <si>
+    <t>387</t>
+  </si>
+  <si>
+    <t>451</t>
+  </si>
+  <si>
+    <t>6/21 (29%)</t>
+  </si>
+  <si>
+    <t>14/26 (54%)</t>
+  </si>
+  <si>
+    <t>-0.42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Deportivo Riestra  vs  Vélez Sarsfield</t>
+  </si>
+  <si>
+    <t>199</t>
+  </si>
+  <si>
+    <t>638</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Rosario Central  vs  Gimnasia y Esgrima</t>
+  </si>
+  <si>
+    <t>271</t>
+  </si>
+  <si>
+    <t>175</t>
+  </si>
+  <si>
+    <t>14/24 (58%)</t>
+  </si>
+  <si>
+    <t>5/10 (50%)</t>
+  </si>
+  <si>
+    <t>-1.37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Huracán  vs  Estudiantes de Río Cuarto</t>
+  </si>
+  <si>
+    <t>1.58</t>
+  </si>
+  <si>
+    <t>0.95</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>187</t>
+  </si>
+  <si>
+    <t>4/14 (29%)</t>
+  </si>
+  <si>
+    <t>0.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Atlético Tucumán  vs  Club Atlético Belgrano</t>
+  </si>
+  <si>
+    <t>224</t>
+  </si>
+  <si>
+    <t>434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  CA Talleres  vs  Central Córdoba</t>
+  </si>
+  <si>
+    <t>614</t>
+  </si>
+  <si>
+    <t>549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Banfield  vs  River Plate</t>
+  </si>
+  <si>
+    <t>3.42</t>
+  </si>
+  <si>
+    <t>0/6 (0%)</t>
+  </si>
+  <si>
+    <t>2.75</t>
+  </si>
+  <si>
+    <t>-0.25</t>
+  </si>
+  <si>
+    <t>-0.41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Argentinos Juniors  vs  Aldosivi</t>
+  </si>
+  <si>
+    <t>585</t>
+  </si>
+  <si>
+    <t>206</t>
+  </si>
+  <si>
+    <t>518</t>
+  </si>
+  <si>
+    <t>0.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  CA Independiente  vs  Gimnasia y Esgrima Mendoza</t>
+  </si>
+  <si>
+    <t>464</t>
+  </si>
+  <si>
+    <t>-2.63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Independiente Rivadavia  vs  Racing Club</t>
+  </si>
+  <si>
+    <t>3.10</t>
+  </si>
+  <si>
+    <t>0.77</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>304</t>
+  </si>
+  <si>
+    <t>7/11 (64%)</t>
+  </si>
+  <si>
+    <t>3.32</t>
+  </si>
+  <si>
+    <t>0.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Defensa y Justicia  vs  Club Atlético Platense</t>
+  </si>
+  <si>
+    <t>408</t>
+  </si>
+  <si>
+    <t>326</t>
+  </si>
+  <si>
+    <t>9/29 (31%)</t>
+  </si>
+  <si>
+    <t>0.27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Estudiantes de La Plata  vs  Newell's Old Boys</t>
+  </si>
+  <si>
+    <t>1.07</t>
+  </si>
+  <si>
+    <t>562</t>
+  </si>
+  <si>
+    <t>0.17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instituto De Córdoba  vs  San Lorenzo</t>
+  </si>
+  <si>
+    <t>262</t>
+  </si>
+  <si>
+    <t>8/22 (36%)</t>
+  </si>
+  <si>
+    <t>-0.43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Tigre  vs  Barracas Central</t>
+  </si>
+  <si>
+    <t>393</t>
+  </si>
+  <si>
+    <t>11/26 (42%)</t>
+  </si>
+  <si>
+    <t>0.08</t>
   </si>
 </sst>
 </file>
@@ -2799,21 +3022,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB0BEC5"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB0BEC5"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB0BEC5"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB0BEC5"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -2837,6 +3045,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB0BEC5"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB0BEC5"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB0BEC5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB0BEC5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2844,36 +3067,36 @@
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -3178,7 +3401,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C657"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -9872,36 +10095,36 @@
     <mergeCell ref="A398:C398"/>
     <mergeCell ref="A205:C205"/>
     <mergeCell ref="A617:C617"/>
+    <mergeCell ref="A293:C293"/>
     <mergeCell ref="A310:C310"/>
     <mergeCell ref="A337:C337"/>
     <mergeCell ref="A73:C73"/>
     <mergeCell ref="A266:C266"/>
     <mergeCell ref="A222:C222"/>
+    <mergeCell ref="A573:C573"/>
+    <mergeCell ref="A600:C600"/>
+    <mergeCell ref="A134:C134"/>
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="A161:C161"/>
     <mergeCell ref="A117:C117"/>
     <mergeCell ref="A249:C249"/>
-    <mergeCell ref="A293:C293"/>
-    <mergeCell ref="A556:C556"/>
-    <mergeCell ref="A470:C470"/>
-    <mergeCell ref="A514:C514"/>
-    <mergeCell ref="A573:C573"/>
-    <mergeCell ref="A600:C600"/>
     <mergeCell ref="A354:C354"/>
     <mergeCell ref="A90:C90"/>
     <mergeCell ref="A426:C426"/>
     <mergeCell ref="A531:C531"/>
+    <mergeCell ref="A556:C556"/>
     <mergeCell ref="A443:C443"/>
     <mergeCell ref="A487:C487"/>
     <mergeCell ref="A381:C381"/>
-    <mergeCell ref="A134:C134"/>
+    <mergeCell ref="A470:C470"/>
+    <mergeCell ref="A514:C514"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C657"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -16597,6 +16820,7 @@
     <mergeCell ref="A441:C441"/>
     <mergeCell ref="A618:C618"/>
     <mergeCell ref="A601:C601"/>
+    <mergeCell ref="A424:C424"/>
     <mergeCell ref="A573:C573"/>
     <mergeCell ref="A380:C380"/>
     <mergeCell ref="A336:C336"/>
@@ -16610,7 +16834,6 @@
     <mergeCell ref="A160:C160"/>
     <mergeCell ref="A116:C116"/>
     <mergeCell ref="A309:C309"/>
-    <mergeCell ref="A424:C424"/>
     <mergeCell ref="A265:C265"/>
     <mergeCell ref="A221:C221"/>
     <mergeCell ref="A485:C485"/>
@@ -23350,10 +23573,10 @@
     <mergeCell ref="A399:C399"/>
     <mergeCell ref="A205:C205"/>
     <mergeCell ref="A646:C646"/>
+    <mergeCell ref="A293:C293"/>
+    <mergeCell ref="A382:C382"/>
     <mergeCell ref="A310:C310"/>
     <mergeCell ref="A337:C337"/>
-    <mergeCell ref="A266:C266"/>
-    <mergeCell ref="A222:C222"/>
     <mergeCell ref="A72:C72"/>
     <mergeCell ref="A134:C134"/>
     <mergeCell ref="A28:C28"/>
@@ -23372,8 +23595,8 @@
     <mergeCell ref="A470:C470"/>
     <mergeCell ref="A514:C514"/>
     <mergeCell ref="A249:C249"/>
-    <mergeCell ref="A293:C293"/>
-    <mergeCell ref="A382:C382"/>
+    <mergeCell ref="A266:C266"/>
+    <mergeCell ref="A222:C222"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -30093,7 +30316,6 @@
     <mergeCell ref="A600:C600"/>
     <mergeCell ref="A72:C72"/>
     <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A484:C484"/>
     <mergeCell ref="A512:C512"/>
     <mergeCell ref="A556:C556"/>
     <mergeCell ref="A116:C116"/>
@@ -30107,6 +30329,7 @@
     <mergeCell ref="A133:C133"/>
     <mergeCell ref="A246:C246"/>
     <mergeCell ref="A89:C89"/>
+    <mergeCell ref="A484:C484"/>
     <mergeCell ref="A351:C351"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -36858,9 +37081,9 @@
   <mergeCells count="30">
     <mergeCell ref="A648:C648"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A45:C45"/>
     <mergeCell ref="A576:C576"/>
     <mergeCell ref="A620:C620"/>
+    <mergeCell ref="A45:C45"/>
     <mergeCell ref="A250:C250"/>
     <mergeCell ref="A399:C399"/>
     <mergeCell ref="A162:C162"/>
@@ -36906,8 +37129,8 @@
       <c r="A3" s="2" t="s">
         <v>814</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="4"/>
     </row>
     <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="5" t="s">
@@ -37200,8 +37423,8 @@
       <c r="A31" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="4"/>
     </row>
     <row r="32" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A32" s="5" t="s">
@@ -37363,8 +37586,8 @@
       <c r="A48" s="2" t="s">
         <v>817</v>
       </c>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="4"/>
     </row>
     <row r="49" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A49" s="5" t="s">
@@ -37624,8 +37847,8 @@
       <c r="A73" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B73" s="14"/>
-      <c r="C73" s="14"/>
+      <c r="B73" s="3"/>
+      <c r="C73" s="4"/>
     </row>
     <row r="74" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A74" s="5" t="s">
@@ -37787,8 +38010,8 @@
       <c r="A90" s="2" t="s">
         <v>819</v>
       </c>
-      <c r="B90" s="14"/>
-      <c r="C90" s="14"/>
+      <c r="B90" s="3"/>
+      <c r="C90" s="4"/>
     </row>
     <row r="91" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A91" s="5" t="s">
@@ -38070,8 +38293,8 @@
       <c r="A117" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B117" s="14"/>
-      <c r="C117" s="14"/>
+      <c r="B117" s="3"/>
+      <c r="C117" s="4"/>
     </row>
     <row r="118" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A118" s="5" t="s">
@@ -38233,8 +38456,8 @@
       <c r="A134" s="2" t="s">
         <v>824</v>
       </c>
-      <c r="B134" s="14"/>
-      <c r="C134" s="14"/>
+      <c r="B134" s="3"/>
+      <c r="C134" s="4"/>
     </row>
     <row r="135" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A135" s="5" t="s">
@@ -38516,8 +38739,8 @@
       <c r="A161" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B161" s="14"/>
-      <c r="C161" s="14"/>
+      <c r="B161" s="3"/>
+      <c r="C161" s="4"/>
     </row>
     <row r="162" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A162" s="5" t="s">
@@ -38679,8 +38902,8 @@
       <c r="A178" s="2" t="s">
         <v>828</v>
       </c>
-      <c r="B178" s="14"/>
-      <c r="C178" s="14"/>
+      <c r="B178" s="3"/>
+      <c r="C178" s="4"/>
     </row>
     <row r="179" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A179" s="5" t="s">
@@ -38962,8 +39185,8 @@
       <c r="A205" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B205" s="14"/>
-      <c r="C205" s="14"/>
+      <c r="B205" s="3"/>
+      <c r="C205" s="4"/>
     </row>
     <row r="206" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A206" s="5" t="s">
@@ -39125,8 +39348,8 @@
       <c r="A222" s="2" t="s">
         <v>833</v>
       </c>
-      <c r="B222" s="14"/>
-      <c r="C222" s="14"/>
+      <c r="B222" s="3"/>
+      <c r="C222" s="4"/>
     </row>
     <row r="223" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A223" s="5" t="s">
@@ -39408,8 +39631,8 @@
       <c r="A249" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B249" s="14"/>
-      <c r="C249" s="14"/>
+      <c r="B249" s="3"/>
+      <c r="C249" s="4"/>
     </row>
     <row r="250" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A250" s="5" t="s">
@@ -39571,8 +39794,8 @@
       <c r="A266" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="B266" s="14"/>
-      <c r="C266" s="14"/>
+      <c r="B266" s="3"/>
+      <c r="C266" s="4"/>
     </row>
     <row r="267" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A267" s="5" t="s">
@@ -39854,8 +40077,8 @@
       <c r="A293" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B293" s="14"/>
-      <c r="C293" s="14"/>
+      <c r="B293" s="3"/>
+      <c r="C293" s="4"/>
     </row>
     <row r="294" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A294" s="5" t="s">
@@ -40017,8 +40240,8 @@
       <c r="A310" s="2" t="s">
         <v>847</v>
       </c>
-      <c r="B310" s="14"/>
-      <c r="C310" s="14"/>
+      <c r="B310" s="3"/>
+      <c r="C310" s="4"/>
     </row>
     <row r="311" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A311" s="5" t="s">
@@ -40300,8 +40523,8 @@
       <c r="A337" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B337" s="14"/>
-      <c r="C337" s="14"/>
+      <c r="B337" s="3"/>
+      <c r="C337" s="4"/>
     </row>
     <row r="338" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A338" s="5" t="s">
@@ -40463,8 +40686,8 @@
       <c r="A354" s="2" t="s">
         <v>852</v>
       </c>
-      <c r="B354" s="14"/>
-      <c r="C354" s="14"/>
+      <c r="B354" s="3"/>
+      <c r="C354" s="4"/>
     </row>
     <row r="355" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A355" s="5" t="s">
@@ -40746,8 +40969,8 @@
       <c r="A381" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B381" s="14"/>
-      <c r="C381" s="14"/>
+      <c r="B381" s="3"/>
+      <c r="C381" s="4"/>
     </row>
     <row r="382" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A382" s="5" t="s">
@@ -40909,8 +41132,8 @@
       <c r="A398" s="2" t="s">
         <v>860</v>
       </c>
-      <c r="B398" s="14"/>
-      <c r="C398" s="14"/>
+      <c r="B398" s="3"/>
+      <c r="C398" s="4"/>
     </row>
     <row r="399" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A399" s="5" t="s">
@@ -41192,8 +41415,8 @@
       <c r="A425" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B425" s="14"/>
-      <c r="C425" s="14"/>
+      <c r="B425" s="3"/>
+      <c r="C425" s="4"/>
     </row>
     <row r="426" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A426" s="5" t="s">
@@ -41355,8 +41578,8 @@
       <c r="A442" s="2" t="s">
         <v>866</v>
       </c>
-      <c r="B442" s="14"/>
-      <c r="C442" s="14"/>
+      <c r="B442" s="3"/>
+      <c r="C442" s="4"/>
     </row>
     <row r="443" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A443" s="5" t="s">
@@ -41638,8 +41861,8 @@
       <c r="A469" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B469" s="14"/>
-      <c r="C469" s="14"/>
+      <c r="B469" s="3"/>
+      <c r="C469" s="4"/>
     </row>
     <row r="470" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A470" s="5" t="s">
@@ -41801,8 +42024,8 @@
       <c r="A486" s="2" t="s">
         <v>870</v>
       </c>
-      <c r="B486" s="14"/>
-      <c r="C486" s="14"/>
+      <c r="B486" s="3"/>
+      <c r="C486" s="4"/>
     </row>
     <row r="487" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A487" s="5" t="s">
@@ -42073,8 +42296,8 @@
       <c r="A512" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B512" s="14"/>
-      <c r="C512" s="14"/>
+      <c r="B512" s="3"/>
+      <c r="C512" s="4"/>
     </row>
     <row r="513" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A513" s="5" t="s">
@@ -42236,8 +42459,8 @@
       <c r="A529" s="2" t="s">
         <v>876</v>
       </c>
-      <c r="B529" s="14"/>
-      <c r="C529" s="14"/>
+      <c r="B529" s="3"/>
+      <c r="C529" s="4"/>
     </row>
     <row r="530" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A530" s="5" t="s">
@@ -42519,8 +42742,8 @@
       <c r="A556" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B556" s="14"/>
-      <c r="C556" s="14"/>
+      <c r="B556" s="3"/>
+      <c r="C556" s="4"/>
     </row>
     <row r="557" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A557" s="5" t="s">
@@ -42682,8 +42905,8 @@
       <c r="A573" s="2" t="s">
         <v>883</v>
       </c>
-      <c r="B573" s="14"/>
-      <c r="C573" s="14"/>
+      <c r="B573" s="3"/>
+      <c r="C573" s="4"/>
     </row>
     <row r="574" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A574" s="5" t="s">
@@ -42965,8 +43188,8 @@
       <c r="A600" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B600" s="14"/>
-      <c r="C600" s="14"/>
+      <c r="B600" s="3"/>
+      <c r="C600" s="4"/>
     </row>
     <row r="601" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A601" s="5" t="s">
@@ -43128,8 +43351,8 @@
       <c r="A617" s="2" t="s">
         <v>890</v>
       </c>
-      <c r="B617" s="14"/>
-      <c r="C617" s="14"/>
+      <c r="B617" s="3"/>
+      <c r="C617" s="4"/>
     </row>
     <row r="618" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A618" s="5" t="s">
@@ -43411,8 +43634,8 @@
       <c r="A644" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B644" s="14"/>
-      <c r="C644" s="14"/>
+      <c r="B644" s="3"/>
+      <c r="C644" s="4"/>
     </row>
     <row r="645" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A645" s="5" t="s">
@@ -43570,36 +43793,6739 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="A644:C644"/>
+    <mergeCell ref="A442:C442"/>
+    <mergeCell ref="A205:C205"/>
+    <mergeCell ref="A617:C617"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A310:C310"/>
+    <mergeCell ref="A337:C337"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A73:C73"/>
+    <mergeCell ref="A266:C266"/>
+    <mergeCell ref="A222:C222"/>
+    <mergeCell ref="A178:C178"/>
     <mergeCell ref="A486:C486"/>
+    <mergeCell ref="A3:C3"/>
     <mergeCell ref="A573:C573"/>
+    <mergeCell ref="A398:C398"/>
+    <mergeCell ref="A529:C529"/>
+    <mergeCell ref="A600:C600"/>
+    <mergeCell ref="A134:C134"/>
+    <mergeCell ref="A161:C161"/>
+    <mergeCell ref="A117:C117"/>
     <mergeCell ref="A293:C293"/>
-    <mergeCell ref="A529:C529"/>
+    <mergeCell ref="A249:C249"/>
+    <mergeCell ref="A354:C354"/>
+    <mergeCell ref="A90:C90"/>
+    <mergeCell ref="A469:C469"/>
+    <mergeCell ref="A512:C512"/>
+    <mergeCell ref="A556:C556"/>
+    <mergeCell ref="A425:C425"/>
     <mergeCell ref="A381:C381"/>
-    <mergeCell ref="A644:C644"/>
-    <mergeCell ref="A512:C512"/>
-    <mergeCell ref="A134:C134"/>
-    <mergeCell ref="A442:C442"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:C657"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="40" style="1" customWidth="1"/>
+    <col min="2" max="3" width="24" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+    </row>
+    <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6">
+        <v>4</v>
+      </c>
+      <c r="C5" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A7" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>581</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A9" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A11" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A12" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A13" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A14" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A15" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A16" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A17" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>894</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A18" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A19" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A20" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A21" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A22" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A23" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A24" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>472</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A25" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A26" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A27" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A28" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="30" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A30" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+    </row>
+    <row r="31" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A31" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A32" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32" s="13">
+        <v>41.7</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A33" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" s="10">
+        <v>54.5</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A34" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B34" s="13">
+        <v>0.107</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A35" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B35" s="10">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A36" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B36" s="13">
+        <v>0</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A37" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B37" s="10">
+        <v>0</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A38" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B38" s="13">
+        <v>0</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A39" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B39" s="10">
+        <v>0</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A40" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B40" s="13">
+        <v>0</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A41" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B41" s="10">
+        <v>0</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A42" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B42" s="13">
+        <v>0.79</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A43" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B43" s="10">
+        <v>58.3</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A44" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B44" s="13">
+        <v>63.6</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="46" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="47" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A47" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="B47" s="14"/>
+      <c r="C47" s="14"/>
+    </row>
+    <row r="48" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A48" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A49" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B49" s="6">
+        <v>1</v>
+      </c>
+      <c r="C49" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A50" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A51" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A52" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A53" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A54" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A55" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A56" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A57" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A58" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A59" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>898</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A60" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>900</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A61" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A62" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A63" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B63" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C63" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A64" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A65" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A66" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A67" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>901</v>
+      </c>
+      <c r="C67" s="10" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A68" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A69" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B69" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C69" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A70" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A71" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B71" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="C71" s="10" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="73" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A73" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B73" s="14"/>
+      <c r="C73" s="14"/>
+    </row>
+    <row r="74" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A74" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A75" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B75" s="13">
+        <v>21.1</v>
+      </c>
+      <c r="C75" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A76" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B76" s="10">
+        <v>20</v>
+      </c>
+      <c r="C76" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A77" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B77" s="13">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="C77" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A78" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B78" s="10">
+        <v>9.0999999999999998E-2</v>
+      </c>
+      <c r="C78" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A79" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B79" s="13">
+        <v>0</v>
+      </c>
+      <c r="C79" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A80" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B80" s="10">
+        <v>0</v>
+      </c>
+      <c r="C80" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A81" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B81" s="13">
+        <v>0</v>
+      </c>
+      <c r="C81" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A82" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B82" s="10">
+        <v>0</v>
+      </c>
+      <c r="C82" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A83" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B83" s="13">
+        <v>0</v>
+      </c>
+      <c r="C83" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A84" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B84" s="10">
+        <v>0</v>
+      </c>
+      <c r="C84" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A85" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B85" s="13">
+        <v>0.25</v>
+      </c>
+      <c r="C85" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A86" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B86" s="10">
+        <v>47.4</v>
+      </c>
+      <c r="C86" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A87" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B87" s="13">
+        <v>70</v>
+      </c>
+      <c r="C87" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="89" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="90" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A90" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="B90" s="14"/>
+      <c r="C90" s="14"/>
+    </row>
+    <row r="91" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A91" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A92" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B92" s="6">
+        <v>1</v>
+      </c>
+      <c r="C92" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A93" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B93" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A94" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B94" s="10" t="s">
+        <v>611</v>
+      </c>
+      <c r="C94" s="10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A95" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B95" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A96" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B96" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A97" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B97" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A98" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B98" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C98" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A99" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B99" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A100" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B100" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C100" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A101" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B101" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A102" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B102" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C102" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A103" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B103" s="8" t="s">
+        <v>905</v>
+      </c>
+      <c r="C103" s="8" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A104" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B104" s="10" t="s">
+        <v>907</v>
+      </c>
+      <c r="C104" s="10" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A105" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B105" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A106" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B106" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C106" s="10" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A107" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B107" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A108" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B108" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="C108" s="10" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A109" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B109" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C109" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A110" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B110" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C110" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A111" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B111" s="8" t="s">
+        <v>760</v>
+      </c>
+      <c r="C111" s="8" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A112" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B112" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A113" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B113" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C113" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A114" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B114" s="10" t="s">
+        <v>509</v>
+      </c>
+      <c r="C114" s="10" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A115" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B115" s="8" t="s">
+        <v>578</v>
+      </c>
+      <c r="C115" s="8" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="117" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A117" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B117" s="14"/>
+      <c r="C117" s="14"/>
+    </row>
+    <row r="118" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A118" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A119" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B119" s="13">
+        <v>42.9</v>
+      </c>
+      <c r="C119" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A120" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B120" s="10">
+        <v>38.5</v>
+      </c>
+      <c r="C120" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A121" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B121" s="13">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="C121" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A122" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B122" s="10">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="C122" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A123" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B123" s="13">
+        <v>0</v>
+      </c>
+      <c r="C123" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A124" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B124" s="10">
+        <v>0</v>
+      </c>
+      <c r="C124" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A125" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B125" s="13">
+        <v>0</v>
+      </c>
+      <c r="C125" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A126" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B126" s="10">
+        <v>0</v>
+      </c>
+      <c r="C126" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A127" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B127" s="13">
+        <v>0</v>
+      </c>
+      <c r="C127" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A128" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B128" s="10">
+        <v>0</v>
+      </c>
+      <c r="C128" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A129" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B129" s="13">
+        <v>0.06</v>
+      </c>
+      <c r="C129" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A130" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B130" s="10">
+        <v>42.9</v>
+      </c>
+      <c r="C130" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A131" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B131" s="13">
+        <v>46.2</v>
+      </c>
+      <c r="C131" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="133" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="134" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A134" s="2" t="s">
+        <v>909</v>
+      </c>
+      <c r="B134" s="14"/>
+      <c r="C134" s="14"/>
+    </row>
+    <row r="135" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A135" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A136" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B136" s="6">
+        <v>1</v>
+      </c>
+      <c r="C136" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A137" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B137" s="8" t="s">
+        <v>620</v>
+      </c>
+      <c r="C137" s="8" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A138" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B138" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="C138" s="10" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A139" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B139" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C139" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A140" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B140" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C140" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A141" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B141" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C141" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A142" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B142" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C142" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A143" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B143" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C143" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A144" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B144" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C144" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A145" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B145" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C145" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A146" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B146" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C146" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A147" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B147" s="8" t="s">
+        <v>590</v>
+      </c>
+      <c r="C147" s="8" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A148" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B148" s="10" t="s">
+        <v>829</v>
+      </c>
+      <c r="C148" s="10" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A149" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B149" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C149" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A150" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B150" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C150" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A151" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B151" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C151" s="8" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A152" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B152" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="C152" s="10" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A153" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B153" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C153" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A154" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B154" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C154" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A155" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B155" s="8" t="s">
+        <v>912</v>
+      </c>
+      <c r="C155" s="8" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A156" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B156" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C156" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A157" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B157" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A158" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B158" s="10" t="s">
+        <v>734</v>
+      </c>
+      <c r="C158" s="10" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A159" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B159" s="8" t="s">
+        <v>914</v>
+      </c>
+      <c r="C159" s="8" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="161" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A161" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B161" s="14"/>
+      <c r="C161" s="14"/>
+    </row>
+    <row r="162" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A162" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A163" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B163" s="13">
+        <v>46.7</v>
+      </c>
+      <c r="C163" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A164" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B164" s="10">
+        <v>27.3</v>
+      </c>
+      <c r="C164" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A165" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B165" s="13">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="C165" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A166" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B166" s="10">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="C166" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A167" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B167" s="13">
+        <v>0</v>
+      </c>
+      <c r="C167" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A168" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B168" s="10">
+        <v>0</v>
+      </c>
+      <c r="C168" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A169" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B169" s="13">
+        <v>0</v>
+      </c>
+      <c r="C169" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A170" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B170" s="10">
+        <v>0</v>
+      </c>
+      <c r="C170" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A171" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B171" s="13">
+        <v>0</v>
+      </c>
+      <c r="C171" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A172" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B172" s="10">
+        <v>0</v>
+      </c>
+      <c r="C172" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A173" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B173" s="13">
+        <v>0.19</v>
+      </c>
+      <c r="C173" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A174" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B174" s="10">
+        <v>80</v>
+      </c>
+      <c r="C174" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A175" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B175" s="13">
+        <v>45.5</v>
+      </c>
+      <c r="C175" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="177" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="178" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A178" s="2" t="s">
+        <v>915</v>
+      </c>
+      <c r="B178" s="14"/>
+      <c r="C178" s="14"/>
+    </row>
+    <row r="179" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A179" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C179" s="5" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A180" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B180" s="6">
+        <v>1</v>
+      </c>
+      <c r="C180" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A181" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B181" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="C181" s="8" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A182" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B182" s="10" t="s">
+        <v>916</v>
+      </c>
+      <c r="C182" s="10" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A183" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B183" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C183" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A184" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B184" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C184" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A185" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B185" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C185" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A186" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B186" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C186" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A187" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B187" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C187" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A188" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B188" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C188" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A189" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B189" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C189" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A190" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B190" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C190" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A191" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B191" s="8" t="s">
+        <v>918</v>
+      </c>
+      <c r="C191" s="8" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A192" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B192" s="10" t="s">
+        <v>538</v>
+      </c>
+      <c r="C192" s="10" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A193" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B193" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C193" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A194" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B194" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C194" s="10" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A195" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B195" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C195" s="8" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A196" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B196" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C196" s="10" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A197" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B197" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C197" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A198" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B198" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C198" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A199" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B199" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="C199" s="8" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A200" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B200" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C200" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A201" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B201" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C201" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A202" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B202" s="10" t="s">
+        <v>638</v>
+      </c>
+      <c r="C202" s="10" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A203" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B203" s="8" t="s">
+        <v>789</v>
+      </c>
+      <c r="C203" s="8" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="205" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A205" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B205" s="14"/>
+      <c r="C205" s="14"/>
+    </row>
+    <row r="206" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A206" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B206" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C206" s="5" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A207" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B207" s="13">
+        <v>11.1</v>
+      </c>
+      <c r="C207" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A208" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B208" s="10">
+        <v>20</v>
+      </c>
+      <c r="C208" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A209" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B209" s="13">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="C209" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A210" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B210" s="10">
+        <v>0.19</v>
+      </c>
+      <c r="C210" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A211" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B211" s="13">
+        <v>0</v>
+      </c>
+      <c r="C211" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A212" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B212" s="10">
+        <v>0</v>
+      </c>
+      <c r="C212" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A213" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B213" s="13">
+        <v>0</v>
+      </c>
+      <c r="C213" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A214" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B214" s="10">
+        <v>0</v>
+      </c>
+      <c r="C214" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A215" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B215" s="13">
+        <v>0</v>
+      </c>
+      <c r="C215" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A216" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B216" s="10">
+        <v>0</v>
+      </c>
+      <c r="C216" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A217" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B217" s="13">
+        <v>0.63</v>
+      </c>
+      <c r="C217" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A218" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B218" s="10">
+        <v>50</v>
+      </c>
+      <c r="C218" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A219" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B219" s="13">
+        <v>80</v>
+      </c>
+      <c r="C219" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="221" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="222" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A222" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="B222" s="14"/>
+      <c r="C222" s="14"/>
+    </row>
+    <row r="223" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A223" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B223" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="C223" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A224" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B224" s="6">
+        <v>0</v>
+      </c>
+      <c r="C224" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A225" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B225" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="C225" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A226" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B226" s="10" t="s">
+        <v>509</v>
+      </c>
+      <c r="C226" s="10" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A227" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B227" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="C227" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A228" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B228" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C228" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A229" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B229" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C229" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A230" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B230" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C230" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A231" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B231" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C231" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A232" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B232" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C232" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A233" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B233" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C233" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A234" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B234" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C234" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A235" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B235" s="8" t="s">
+        <v>878</v>
+      </c>
+      <c r="C235" s="8" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A236" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B236" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="C236" s="10" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A237" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B237" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C237" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A238" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B238" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C238" s="10" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A239" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B239" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C239" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A240" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B240" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C240" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A241" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B241" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C241" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A242" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B242" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C242" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A243" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B243" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="C243" s="8" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A244" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B244" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C244" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A245" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B245" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C245" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A246" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B246" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="C246" s="10" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A247" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B247" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="C247" s="8" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="249" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A249" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B249" s="14"/>
+      <c r="C249" s="14"/>
+    </row>
+    <row r="250" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A250" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B250" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="C250" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A251" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B251" s="13">
+        <v>12.5</v>
+      </c>
+      <c r="C251" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A252" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B252" s="10">
+        <v>30</v>
+      </c>
+      <c r="C252" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A253" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B253" s="13">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="C253" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A254" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B254" s="10">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="C254" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A255" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B255" s="13">
+        <v>0</v>
+      </c>
+      <c r="C255" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A256" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B256" s="10">
+        <v>0</v>
+      </c>
+      <c r="C256" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A257" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B257" s="13">
+        <v>0</v>
+      </c>
+      <c r="C257" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A258" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B258" s="10">
+        <v>0</v>
+      </c>
+      <c r="C258" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A259" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B259" s="13">
+        <v>0</v>
+      </c>
+      <c r="C259" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A260" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B260" s="10">
+        <v>0</v>
+      </c>
+      <c r="C260" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A261" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B261" s="13">
+        <v>0.02</v>
+      </c>
+      <c r="C261" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A262" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B262" s="10">
+        <v>62.5</v>
+      </c>
+      <c r="C262" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A263" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B263" s="13">
+        <v>60</v>
+      </c>
+      <c r="C263" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="265" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="266" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A266" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="B266" s="14"/>
+      <c r="C266" s="14"/>
+    </row>
+    <row r="267" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A267" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B267" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C267" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A268" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B268" s="6">
+        <v>0</v>
+      </c>
+      <c r="C268" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A269" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B269" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C269" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A270" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B270" s="10" t="s">
+        <v>779</v>
+      </c>
+      <c r="C270" s="10" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A271" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B271" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="C271" s="8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A272" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B272" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C272" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A273" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B273" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C273" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A274" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B274" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C274" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A275" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B275" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C275" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A276" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B276" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C276" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A277" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B277" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C277" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A278" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B278" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C278" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A279" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B279" s="8" t="s">
+        <v>926</v>
+      </c>
+      <c r="C279" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A280" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B280" s="10" t="s">
+        <v>927</v>
+      </c>
+      <c r="C280" s="10" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A281" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B281" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C281" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A282" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B282" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C282" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A283" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B283" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C283" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A284" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B284" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C284" s="10" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A285" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B285" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C285" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A286" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B286" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C286" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A287" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B287" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="C287" s="8" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A288" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B288" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C288" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A289" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B289" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C289" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A290" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B290" s="10" t="s">
+        <v>823</v>
+      </c>
+      <c r="C290" s="10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A291" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B291" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C291" s="8" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="293" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A293" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B293" s="14"/>
+      <c r="C293" s="14"/>
+    </row>
+    <row r="294" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A294" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B294" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C294" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A295" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B295" s="13">
+        <v>20.8</v>
+      </c>
+      <c r="C295" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A296" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B296" s="10">
+        <v>25</v>
+      </c>
+      <c r="C296" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A297" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B297" s="13">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="C297" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A298" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B298" s="10">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="C298" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A299" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B299" s="13">
+        <v>0</v>
+      </c>
+      <c r="C299" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A300" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B300" s="10">
+        <v>0</v>
+      </c>
+      <c r="C300" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A301" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B301" s="13">
+        <v>0</v>
+      </c>
+      <c r="C301" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A302" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B302" s="10">
+        <v>0</v>
+      </c>
+      <c r="C302" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A303" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B303" s="13">
+        <v>0</v>
+      </c>
+      <c r="C303" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A304" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B304" s="10">
+        <v>0</v>
+      </c>
+      <c r="C304" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A305" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B305" s="13">
+        <v>-0.22</v>
+      </c>
+      <c r="C305" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A306" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B306" s="10">
+        <v>54.2</v>
+      </c>
+      <c r="C306" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A307" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B307" s="13">
+        <v>56.2</v>
+      </c>
+      <c r="C307" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="309" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="310" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A310" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="B310" s="14"/>
+      <c r="C310" s="14"/>
+    </row>
+    <row r="311" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A311" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B311" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C311" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A312" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B312" s="6">
+        <v>2</v>
+      </c>
+      <c r="C312" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A313" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B313" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="C313" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A314" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B314" s="10" t="s">
+        <v>665</v>
+      </c>
+      <c r="C314" s="10" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A315" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B315" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C315" s="8" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A316" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B316" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C316" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A317" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B317" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C317" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A318" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B318" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C318" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A319" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B319" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C319" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A320" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B320" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C320" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A321" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B321" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C321" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A322" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B322" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C322" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A323" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B323" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="C323" s="8" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A324" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B324" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="C324" s="10" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A325" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B325" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C325" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A326" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B326" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C326" s="10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A327" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B327" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C327" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A328" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B328" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="C328" s="10" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A329" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B329" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C329" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A330" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B330" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C330" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A331" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B331" s="8" t="s">
+        <v>930</v>
+      </c>
+      <c r="C331" s="8" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A332" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B332" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C332" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A333" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B333" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C333" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A334" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B334" s="10" t="s">
+        <v>475</v>
+      </c>
+      <c r="C334" s="10" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A335" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B335" s="8" t="s">
+        <v>932</v>
+      </c>
+      <c r="C335" s="8" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="337" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A337" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B337" s="14"/>
+      <c r="C337" s="14"/>
+    </row>
+    <row r="338" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A338" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B338" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C338" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A339" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B339" s="13">
+        <v>35.700000000000003</v>
+      </c>
+      <c r="C339" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A340" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B340" s="10">
+        <v>42.1</v>
+      </c>
+      <c r="C340" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A341" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B341" s="13">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="C341" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A342" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B342" s="10">
+        <v>0.18</v>
+      </c>
+      <c r="C342" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A343" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B343" s="13">
+        <v>0</v>
+      </c>
+      <c r="C343" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A344" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B344" s="10">
+        <v>0</v>
+      </c>
+      <c r="C344" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A345" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B345" s="13">
+        <v>0</v>
+      </c>
+      <c r="C345" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A346" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B346" s="10">
+        <v>0</v>
+      </c>
+      <c r="C346" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A347" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B347" s="13">
+        <v>0</v>
+      </c>
+      <c r="C347" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A348" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B348" s="10">
+        <v>0</v>
+      </c>
+      <c r="C348" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A349" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B349" s="13">
+        <v>-2.25</v>
+      </c>
+      <c r="C349" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A350" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B350" s="10">
+        <v>57.1</v>
+      </c>
+      <c r="C350" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A351" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B351" s="13">
+        <v>68.400000000000006</v>
+      </c>
+      <c r="C351" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="353" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="354" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A354" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="B354" s="14"/>
+      <c r="C354" s="14"/>
+    </row>
+    <row r="355" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A355" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B355" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C355" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A356" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B356" s="6">
+        <v>2</v>
+      </c>
+      <c r="C356" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A357" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B357" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="C357" s="8" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A358" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B358" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="C358" s="10" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A359" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B359" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="C359" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A360" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B360" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C360" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A361" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B361" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C361" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A362" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B362" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C362" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A363" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B363" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C363" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A364" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B364" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C364" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A365" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B365" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C365" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A366" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B366" s="10" t="s">
+        <v>935</v>
+      </c>
+      <c r="C366" s="10" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A367" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B367" s="8" t="s">
+        <v>937</v>
+      </c>
+      <c r="C367" s="8" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A368" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B368" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C368" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A369" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B369" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="C369" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A370" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B370" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C370" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A371" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B371" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C371" s="8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A372" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B372" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C372" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A373" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B373" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C373" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A374" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B374" s="10" t="s">
+        <v>490</v>
+      </c>
+      <c r="C374" s="10" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A375" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B375" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C375" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A376" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B376" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C376" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A377" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B377" s="8" t="s">
+        <v>556</v>
+      </c>
+      <c r="C377" s="8" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A378" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B378" s="10" t="s">
+        <v>646</v>
+      </c>
+      <c r="C378" s="10" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="380" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A380" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B380" s="14"/>
+      <c r="C380" s="14"/>
+    </row>
+    <row r="381" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A381" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B381" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C381" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A382" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B382" s="13">
+        <v>29.2</v>
+      </c>
+      <c r="C382" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A383" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B383" s="10">
+        <v>28.6</v>
+      </c>
+      <c r="C383" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A384" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B384" s="13">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="C384" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A385" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B385" s="10">
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="C385" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A386" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B386" s="13">
+        <v>0</v>
+      </c>
+      <c r="C386" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A387" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B387" s="10">
+        <v>0</v>
+      </c>
+      <c r="C387" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A388" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B388" s="13">
+        <v>0</v>
+      </c>
+      <c r="C388" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A389" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B389" s="10">
+        <v>0</v>
+      </c>
+      <c r="C389" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A390" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B390" s="13">
+        <v>0</v>
+      </c>
+      <c r="C390" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A391" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B391" s="10">
+        <v>0</v>
+      </c>
+      <c r="C391" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A392" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B392" s="13">
+        <v>1.05</v>
+      </c>
+      <c r="C392" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A393" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B393" s="10">
+        <v>62.5</v>
+      </c>
+      <c r="C393" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A394" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B394" s="13">
+        <v>57.1</v>
+      </c>
+      <c r="C394" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="396" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="397" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A397" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="B397" s="14"/>
+      <c r="C397" s="14"/>
+    </row>
+    <row r="398" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A398" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B398" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="C398" s="5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A399" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B399" s="6">
+        <v>0</v>
+      </c>
+      <c r="C399" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A400" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B400" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="C400" s="8" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A401" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B401" s="10" t="s">
+        <v>566</v>
+      </c>
+      <c r="C401" s="10" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A402" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B402" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C402" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A403" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B403" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C403" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A404" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B404" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C404" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A405" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B405" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C405" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A406" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B406" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C406" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A407" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B407" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C407" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A408" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B408" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C408" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A409" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B409" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C409" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A410" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B410" s="8" t="s">
+        <v>940</v>
+      </c>
+      <c r="C410" s="8" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A411" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B411" s="10" t="s">
+        <v>777</v>
+      </c>
+      <c r="C411" s="10" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A412" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B412" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C412" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A413" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B413" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C413" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A414" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B414" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C414" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A415" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B415" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C415" s="10" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A416" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B416" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C416" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A417" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B417" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C417" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A418" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B418" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="C418" s="8" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A419" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B419" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C419" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A420" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B420" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C420" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A421" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B421" s="10" t="s">
+        <v>638</v>
+      </c>
+      <c r="C421" s="10" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A422" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B422" s="8" t="s">
+        <v>941</v>
+      </c>
+      <c r="C422" s="8" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="424" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A424" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B424" s="14"/>
+      <c r="C424" s="14"/>
+    </row>
+    <row r="425" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A425" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B425" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="C425" s="5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A426" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B426" s="13">
+        <v>36.4</v>
+      </c>
+      <c r="C426" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A427" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B427" s="10">
+        <v>36.4</v>
+      </c>
+      <c r="C427" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A428" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B428" s="13">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="C428" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A429" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B429" s="10">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="C429" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A430" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B430" s="13">
+        <v>0</v>
+      </c>
+      <c r="C430" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A431" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B431" s="10">
+        <v>0</v>
+      </c>
+      <c r="C431" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A432" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B432" s="13">
+        <v>0</v>
+      </c>
+      <c r="C432" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A433" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B433" s="10">
+        <v>0</v>
+      </c>
+      <c r="C433" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A434" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B434" s="13">
+        <v>0</v>
+      </c>
+      <c r="C434" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A435" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B435" s="10">
+        <v>0</v>
+      </c>
+      <c r="C435" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A436" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B436" s="13">
+        <v>0.24</v>
+      </c>
+      <c r="C436" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A437" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B437" s="10">
+        <v>63.6</v>
+      </c>
+      <c r="C437" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A438" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B438" s="13">
+        <v>36.4</v>
+      </c>
+      <c r="C438" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="440" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="441" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A441" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="B441" s="14"/>
+      <c r="C441" s="14"/>
+    </row>
+    <row r="442" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A442" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B442" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="C442" s="5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A443" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B443" s="6">
+        <v>3</v>
+      </c>
+      <c r="C443" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A444" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B444" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="C444" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A445" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B445" s="10" t="s">
+        <v>943</v>
+      </c>
+      <c r="C445" s="10" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A446" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B446" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C446" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A447" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B447" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C447" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A448" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B448" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C448" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A449" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B449" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C449" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A450" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B450" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C450" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A451" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B451" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C451" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A452" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B452" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C452" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A453" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B453" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C453" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A454" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B454" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="C454" s="8" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A455" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B455" s="10" t="s">
+        <v>945</v>
+      </c>
+      <c r="C455" s="10" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A456" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B456" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C456" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A457" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B457" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C457" s="10" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A458" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B458" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C458" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="459" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A459" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B459" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="C459" s="10" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A460" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B460" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C460" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A461" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B461" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C461" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="462" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A462" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B462" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C462" s="8" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="463" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A463" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B463" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C463" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="464" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A464" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B464" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C464" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A465" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B465" s="10" t="s">
+        <v>948</v>
+      </c>
+      <c r="C465" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A466" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B466" s="8" t="s">
+        <v>949</v>
+      </c>
+      <c r="C466" s="8" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="468" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A468" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B468" s="14"/>
+      <c r="C468" s="14"/>
+    </row>
+    <row r="469" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A469" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B469" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="C469" s="5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="470" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A470" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B470" s="13">
+        <v>47.4</v>
+      </c>
+      <c r="C470" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="471" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A471" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B471" s="10">
+        <v>36.4</v>
+      </c>
+      <c r="C471" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="472" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A472" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B472" s="13">
+        <v>0.16300000000000001</v>
+      </c>
+      <c r="C472" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A473" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B473" s="10">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="C473" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A474" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B474" s="13">
+        <v>0</v>
+      </c>
+      <c r="C474" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="475" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A475" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B475" s="10">
+        <v>0</v>
+      </c>
+      <c r="C475" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A476" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B476" s="13">
+        <v>0</v>
+      </c>
+      <c r="C476" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A477" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B477" s="10">
+        <v>0</v>
+      </c>
+      <c r="C477" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A478" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B478" s="13">
+        <v>0</v>
+      </c>
+      <c r="C478" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A479" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B479" s="10">
+        <v>0</v>
+      </c>
+      <c r="C479" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A480" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B480" s="13">
+        <v>2.33</v>
+      </c>
+      <c r="C480" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A481" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B481" s="10">
+        <v>57.9</v>
+      </c>
+      <c r="C481" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A482" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B482" s="13">
+        <v>54.5</v>
+      </c>
+      <c r="C482" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="484" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="485" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A485" s="2" t="s">
+        <v>950</v>
+      </c>
+      <c r="B485" s="14"/>
+      <c r="C485" s="14"/>
+    </row>
+    <row r="486" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A486" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B486" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C486" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A487" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B487" s="6">
+        <v>1</v>
+      </c>
+      <c r="C487" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A488" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B488" s="8" t="s">
+        <v>605</v>
+      </c>
+      <c r="C488" s="8" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A489" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B489" s="10" t="s">
+        <v>709</v>
+      </c>
+      <c r="C489" s="10" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A490" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B490" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C490" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A491" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B491" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C491" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A492" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B492" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C492" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A493" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B493" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C493" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A494" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B494" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C494" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A495" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B495" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C495" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A496" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B496" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C496" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A497" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B497" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C497" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="498" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A498" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B498" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C498" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A499" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B499" s="10" t="s">
+        <v>951</v>
+      </c>
+      <c r="C499" s="10" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A500" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B500" s="8" t="s">
+        <v>952</v>
+      </c>
+      <c r="C500" s="8" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="501" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A501" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B501" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C501" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="502" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A502" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B502" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="C502" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A503" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B503" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C503" s="10" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A504" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B504" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="C504" s="8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="505" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A505" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B505" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C505" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="506" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A506" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B506" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C506" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="507" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A507" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B507" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="C507" s="10" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="508" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A508" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B508" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C508" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="509" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A509" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B509" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C509" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="510" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A510" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B510" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="C510" s="8" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="511" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A511" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B511" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="C511" s="10" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="512" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="513" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A513" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B513" s="14"/>
+      <c r="C513" s="14"/>
+    </row>
+    <row r="514" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A514" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B514" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C514" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="515" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A515" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B515" s="13">
+        <v>30</v>
+      </c>
+      <c r="C515" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="516" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A516" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B516" s="10">
+        <v>23.1</v>
+      </c>
+      <c r="C516" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="517" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A517" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B517" s="13">
+        <v>0.108</v>
+      </c>
+      <c r="C517" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="518" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A518" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B518" s="10">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="C518" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="519" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A519" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B519" s="13">
+        <v>0</v>
+      </c>
+      <c r="C519" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="520" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A520" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B520" s="10">
+        <v>0</v>
+      </c>
+      <c r="C520" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="521" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A521" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B521" s="13">
+        <v>0</v>
+      </c>
+      <c r="C521" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="522" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A522" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B522" s="10">
+        <v>0</v>
+      </c>
+      <c r="C522" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="523" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A523" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B523" s="13">
+        <v>0</v>
+      </c>
+      <c r="C523" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="524" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A524" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B524" s="10">
+        <v>0</v>
+      </c>
+      <c r="C524" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="525" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A525" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B525" s="13">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="C525" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="526" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A526" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B526" s="10">
+        <v>60</v>
+      </c>
+      <c r="C526" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="527" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A527" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B527" s="13">
+        <v>53.8</v>
+      </c>
+      <c r="C527" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="528" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="529" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="530" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A530" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="B530" s="14"/>
+      <c r="C530" s="14"/>
+    </row>
+    <row r="531" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A531" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B531" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="C531" s="5" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="532" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A532" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B532" s="6">
+        <v>0</v>
+      </c>
+      <c r="C532" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="533" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A533" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B533" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C533" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="534" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A534" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B534" s="10" t="s">
+        <v>537</v>
+      </c>
+      <c r="C534" s="10" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="535" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A535" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B535" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="C535" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="536" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A536" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B536" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C536" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="537" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A537" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B537" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C537" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="538" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A538" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B538" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C538" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="539" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A539" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B539" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C539" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="540" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A540" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B540" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C540" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="541" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A541" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B541" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C541" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="542" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A542" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B542" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C542" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="543" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A543" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B543" s="8" t="s">
+        <v>957</v>
+      </c>
+      <c r="C543" s="8" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="544" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A544" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B544" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="C544" s="10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="545" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A545" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B545" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C545" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="546" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A546" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B546" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="C546" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="547" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A547" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B547" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C547" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A548" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B548" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C548" s="10" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="549" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A549" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B549" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C549" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="550" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A550" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B550" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C550" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="551" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A551" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B551" s="8" t="s">
+        <v>826</v>
+      </c>
+      <c r="C551" s="8" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="552" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A552" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B552" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C552" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="553" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A553" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B553" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C553" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="554" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A554" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B554" s="10" t="s">
+        <v>537</v>
+      </c>
+      <c r="C554" s="10" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="555" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A555" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B555" s="8" t="s">
+        <v>958</v>
+      </c>
+      <c r="C555" s="8" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="556" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="557" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A557" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B557" s="14"/>
+      <c r="C557" s="14"/>
+    </row>
+    <row r="558" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A558" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B558" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="C558" s="5" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="559" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A559" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B559" s="13">
+        <v>37.5</v>
+      </c>
+      <c r="C559" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A560" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B560" s="10">
+        <v>22.2</v>
+      </c>
+      <c r="C560" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="561" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A561" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B561" s="13">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="C561" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="562" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A562" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B562" s="10">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="C562" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="563" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A563" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B563" s="13">
+        <v>0</v>
+      </c>
+      <c r="C563" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="564" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A564" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B564" s="10">
+        <v>0</v>
+      </c>
+      <c r="C564" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="565" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A565" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B565" s="13">
+        <v>0</v>
+      </c>
+      <c r="C565" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="566" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A566" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B566" s="10">
+        <v>0</v>
+      </c>
+      <c r="C566" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="567" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A567" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B567" s="13">
+        <v>0</v>
+      </c>
+      <c r="C567" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="568" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A568" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B568" s="10">
+        <v>0</v>
+      </c>
+      <c r="C568" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="569" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A569" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B569" s="13">
+        <v>0.96</v>
+      </c>
+      <c r="C569" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="570" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A570" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B570" s="10">
+        <v>70.8</v>
+      </c>
+      <c r="C570" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="571" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A571" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B571" s="13">
+        <v>44.4</v>
+      </c>
+      <c r="C571" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="572" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="573" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="574" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A574" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="B574" s="14"/>
+      <c r="C574" s="14"/>
+    </row>
+    <row r="575" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A575" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B575" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C575" s="5" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="576" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A576" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B576" s="6">
+        <v>1</v>
+      </c>
+      <c r="C576" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="577" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A577" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B577" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="C577" s="8" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="578" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A578" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B578" s="10" t="s">
+        <v>475</v>
+      </c>
+      <c r="C578" s="10" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="579" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A579" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B579" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C579" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="580" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A580" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B580" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C580" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="581" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A581" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B581" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C581" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="582" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A582" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B582" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C582" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="583" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A583" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B583" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C583" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="584" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A584" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B584" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C584" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="585" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A585" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B585" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C585" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="586" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A586" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B586" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C586" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="587" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A587" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B587" s="8" t="s">
+        <v>741</v>
+      </c>
+      <c r="C587" s="8" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="588" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A588" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B588" s="10" t="s">
+        <v>960</v>
+      </c>
+      <c r="C588" s="10" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="589" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A589" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B589" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C589" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="590" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A590" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B590" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="C590" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="591" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A591" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B591" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C591" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="592" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A592" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B592" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C592" s="10" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="593" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A593" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B593" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C593" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="594" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A594" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B594" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C594" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="595" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A595" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B595" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="C595" s="8" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="596" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A596" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B596" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C596" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="597" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A597" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B597" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C597" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="598" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A598" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B598" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="C598" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="599" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A599" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B599" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C599" s="8" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="600" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="601" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A601" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B601" s="14"/>
+      <c r="C601" s="14"/>
+    </row>
+    <row r="602" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A602" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B602" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C602" s="5" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="603" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A603" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B603" s="13">
+        <v>15.8</v>
+      </c>
+      <c r="C603" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="604" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A604" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B604" s="10">
+        <v>20</v>
+      </c>
+      <c r="C604" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="605" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A605" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B605" s="13">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="C605" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="606" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A606" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B606" s="10">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="C606" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="607" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A607" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B607" s="13">
+        <v>0</v>
+      </c>
+      <c r="C607" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="608" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A608" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B608" s="10">
+        <v>0</v>
+      </c>
+      <c r="C608" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="609" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A609" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B609" s="13">
+        <v>0</v>
+      </c>
+      <c r="C609" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="610" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A610" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B610" s="10">
+        <v>0</v>
+      </c>
+      <c r="C610" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="611" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A611" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B611" s="13">
+        <v>0</v>
+      </c>
+      <c r="C611" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="612" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A612" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B612" s="10">
+        <v>0</v>
+      </c>
+      <c r="C612" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="613" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A613" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B613" s="13">
+        <v>1.31</v>
+      </c>
+      <c r="C613" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="614" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A614" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B614" s="10">
+        <v>68.400000000000006</v>
+      </c>
+      <c r="C614" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="615" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A615" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B615" s="13">
+        <v>40</v>
+      </c>
+      <c r="C615" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="616" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="617" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="618" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A618" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="B618" s="14"/>
+      <c r="C618" s="14"/>
+    </row>
+    <row r="619" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A619" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B619" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="C619" s="5" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="620" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A620" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B620" s="6">
+        <v>0</v>
+      </c>
+      <c r="C620" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="621" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A621" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B621" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="C621" s="8" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="622" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A622" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B622" s="10" t="s">
+        <v>954</v>
+      </c>
+      <c r="C622" s="10" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="623" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A623" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B623" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C623" s="8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="624" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A624" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B624" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C624" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="625" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A625" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B625" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C625" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="626" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A626" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B626" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C626" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="627" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A627" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B627" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C627" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="628" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A628" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B628" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C628" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="629" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A629" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B629" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C629" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="630" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A630" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B630" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C630" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="631" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A631" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B631" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="C631" s="8" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="632" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A632" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B632" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C632" s="10" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="633" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A633" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B633" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C633" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="634" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A634" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B634" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C634" s="10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="635" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A635" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B635" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C635" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="636" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A636" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B636" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C636" s="10" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="637" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A637" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B637" s="8" t="s">
+        <v>965</v>
+      </c>
+      <c r="C637" s="8" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="638" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A638" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B638" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C638" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="639" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A639" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B639" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C639" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="640" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A640" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B640" s="10" t="s">
+        <v>966</v>
+      </c>
+      <c r="C640" s="10" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="641" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A641" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B641" s="8" t="s">
+        <v>720</v>
+      </c>
+      <c r="C641" s="8" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="642" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="643" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A643" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B643" s="14"/>
+      <c r="C643" s="14"/>
+    </row>
+    <row r="644" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A644" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B644" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="C644" s="5" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="645" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A645" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B645" s="13">
+        <v>16.7</v>
+      </c>
+      <c r="C645" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="646" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A646" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B646" s="10">
+        <v>14.3</v>
+      </c>
+      <c r="C646" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="647" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A647" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B647" s="13">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="C647" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="648" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A648" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B648" s="10">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="C648" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="649" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A649" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B649" s="13">
+        <v>0</v>
+      </c>
+      <c r="C649" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="650" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A650" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B650" s="10">
+        <v>0</v>
+      </c>
+      <c r="C650" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="651" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A651" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B651" s="13">
+        <v>0</v>
+      </c>
+      <c r="C651" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="652" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A652" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B652" s="10">
+        <v>0</v>
+      </c>
+      <c r="C652" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="653" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A653" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B653" s="13">
+        <v>0</v>
+      </c>
+      <c r="C653" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="654" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A654" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B654" s="10">
+        <v>0</v>
+      </c>
+      <c r="C654" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="655" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A655" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B655" s="13">
+        <v>-0.34</v>
+      </c>
+      <c r="C655" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="656" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A656" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B656" s="10">
+        <v>50</v>
+      </c>
+      <c r="C656" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="657" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A657" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B657" s="13">
+        <v>42.9</v>
+      </c>
+      <c r="C657" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="30">
+    <mergeCell ref="A293:C293"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A485:C485"/>
+    <mergeCell ref="A618:C618"/>
+    <mergeCell ref="A643:C643"/>
+    <mergeCell ref="A441:C441"/>
+    <mergeCell ref="A513:C513"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A161:C161"/>
+    <mergeCell ref="A601:C601"/>
+    <mergeCell ref="A468:C468"/>
+    <mergeCell ref="A73:C73"/>
+    <mergeCell ref="A380:C380"/>
+    <mergeCell ref="A574:C574"/>
+    <mergeCell ref="A557:C557"/>
     <mergeCell ref="A222:C222"/>
     <mergeCell ref="A266:C266"/>
     <mergeCell ref="A178:C178"/>
-    <mergeCell ref="A398:C398"/>
+    <mergeCell ref="A90:C90"/>
     <mergeCell ref="A249:C249"/>
     <mergeCell ref="A354:C354"/>
-    <mergeCell ref="A556:C556"/>
-    <mergeCell ref="A600:C600"/>
-    <mergeCell ref="A469:C469"/>
-    <mergeCell ref="A161:C161"/>
-    <mergeCell ref="A425:C425"/>
-    <mergeCell ref="A617:C617"/>
+    <mergeCell ref="A117:C117"/>
+    <mergeCell ref="A424:C424"/>
+    <mergeCell ref="A134:C134"/>
+    <mergeCell ref="A30:C30"/>
     <mergeCell ref="A205:C205"/>
     <mergeCell ref="A337:C337"/>
-    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A530:C530"/>
     <mergeCell ref="A310:C310"/>
-    <mergeCell ref="A117:C117"/>
-    <mergeCell ref="A90:C90"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A73:C73"/>
+    <mergeCell ref="A397:C397"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
